--- a/data/processed/gyeongnam_high_schools_policy_feedback_refined.xlsx
+++ b/data/processed/gyeongnam_high_schools_policy_feedback_refined.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB147"/>
+  <dimension ref="A1:Z147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,16 +550,6 @@
           <t>policy_strategy_description</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>school_latitude</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>school_longitude</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -592,7 +582,7 @@
         <v>0.1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -604,10 +594,10 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.4444333333333333</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4</v>
+        <v>0.4111</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -641,7 +631,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.433)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.400로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.444)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.411로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -673,12 +663,6 @@
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA2" t="n">
-        <v>35.6771045634292</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>127.689678766522</v>
       </c>
     </row>
     <row r="3">
@@ -712,7 +696,7 @@
         <v>0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I3" t="n">
         <v>0.032183814105257</v>
@@ -724,10 +708,10 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4289345541140421</v>
+        <v>0.4400345541140422</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3956012207807088</v>
+        <v>0.4067012207807089</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -761,7 +745,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.429)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.396로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.440)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.407로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -793,12 +777,6 @@
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA3" t="n">
-        <v>35.0635785835826</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>127.961314511887</v>
       </c>
     </row>
     <row r="4">
@@ -832,7 +810,7 @@
         <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I4" t="n">
         <v>0.3477738096487907</v>
@@ -844,10 +822,10 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2159246032162635</v>
+        <v>0.2270246032162636</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1825912698829302</v>
+        <v>0.1936912698829303</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -881,7 +859,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.216)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.183로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.227)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.194로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -913,23 +891,17 @@
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA4" t="n">
-        <v>35.2759243075308</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>127.834645753809</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>480041680</t>
+          <t>480041912</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>마산제일고등학교</t>
+          <t>칠원고등학교</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -939,7 +911,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>함안군</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -949,25 +921,25 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0064036137928232</v>
+        <v>0.2179458060877966</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1275259674859008</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.1333333333333333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.377976527092908</v>
+        <v>0.2948819353625988</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1446431937595747</v>
+        <v>0.1615486020292655</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -981,12 +953,12 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -996,12 +968,12 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.378)가 상담공급지수(CSI=0.233)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.145로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.295)가 상담공급지수(CSI=0.133)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.162로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -1026,19 +998,13 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>priority:최우선지원; weak:상담인력부족; matrix:인프라취약</t>
+          <t>priority:최우선지원; weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA5" t="n">
-        <v>35.2617842731966</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>128.505456829439</v>
       </c>
     </row>
     <row r="6">
@@ -1072,7 +1038,7 @@
         <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I6" t="n">
         <v>0.2283316038840079</v>
@@ -1084,10 +1050,10 @@
         <v>0.03333333333333333</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1761105346280026</v>
+        <v>0.1872105346280026</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1427772012946693</v>
+        <v>0.1538772012946693</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -1121,7 +1087,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.176)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.143로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.187)가 상담공급지수(CSI=0.033)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.154로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1153,23 +1119,17 @@
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA6" t="n">
-        <v>35.1781655104234</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>127.884595688995</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>480041912</t>
+          <t>480041680</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>칠원고등학교</t>
+          <t>마산제일고등학교</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1179,7 +1139,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>함안군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1189,25 +1149,25 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H7" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2179458060877966</v>
+        <v>0.0064036137928232</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.1275259674859008</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1333333333333333</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2726486020292655</v>
+        <v>0.377976527092908</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1393152686959322</v>
+        <v>0.1446431937595747</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1221,7 +1181,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1236,12 +1196,12 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.273)가 상담공급지수(CSI=0.133)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.139로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.378)가 상담공급지수(CSI=0.233)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.145로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1266,19 +1226,13 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>priority:최우선지원; weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
+          <t>priority:최우선지원; weak:상담인력부족; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA7" t="n">
-        <v>35.3181927290868</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>128.507314800732</v>
       </c>
     </row>
     <row r="8">
@@ -1394,12 +1348,6 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA8" t="n">
-        <v>35.4141721719533</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>129.174394631319</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1514,22 +1462,16 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA9" t="n">
-        <v>35.1014406602207</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>128.819449842833</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>480041788</t>
+          <t>480041660</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>효암고등학교</t>
+          <t>남해해성고등학교</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1539,35 +1481,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>남해군</t>
         </is>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2062807374204296</v>
+        <v>0.2281883551218987</v>
       </c>
       <c r="J10" t="n">
-        <v>0.09879755922469491</v>
+        <v>0.02564102564102564</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.2333333333333333</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4350260988817081</v>
+        <v>0.3068431269209748</v>
       </c>
       <c r="M10" t="n">
-        <v>0.06835943221504143</v>
+        <v>0.07350979358764151</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1576,7 +1518,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 낮음</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1586,7 +1528,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1596,12 +1538,12 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.435)가 상담공급지수(CSI=0.367)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.068로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.307)가 상담공급지수(CSI=0.233)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.074로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1626,19 +1568,13 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>priority:최우선지원; weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
+          <t>priority:최우선지원; weak:상담인력부족; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA10" t="n">
-        <v>35.4123803282307</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>129.16999212693</v>
       </c>
     </row>
     <row r="11">
@@ -1672,7 +1608,7 @@
         <v>0.1</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I11" t="n">
         <v>0.78680479825518</v>
@@ -1684,10 +1620,10 @@
         <v>0.3666666666666667</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4275264894494527</v>
+        <v>0.4386264894494527</v>
       </c>
       <c r="M11" t="n">
-        <v>0.06085982278278601</v>
+        <v>0.07195982278278601</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1721,7 +1657,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.428)가 상담공급지수(CSI=0.367)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.061로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.439)가 상담공급지수(CSI=0.367)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.072로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1753,23 +1689,17 @@
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA11" t="n">
-        <v>35.1696561814851</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>128.281667952322</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>480041660</t>
+          <t>480041788</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>남해해성고등학교</t>
+          <t>효암고등학교</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1779,35 +1709,35 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>남해군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
       <c r="H12" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2281883551218987</v>
+        <v>0.2062807374204296</v>
       </c>
       <c r="J12" t="n">
-        <v>0.02564102564102564</v>
+        <v>0.09879755922469491</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2333333333333333</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2846097935876414</v>
+        <v>0.4350260988817081</v>
       </c>
       <c r="M12" t="n">
-        <v>0.05127646025430807</v>
+        <v>0.06835943221504143</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1816,17 +1746,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>공급 낮음</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1836,12 +1766,12 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 상담수요지수가 상담공급지수보다 높아 우선 지원 검토 필요</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.285)가 상담공급지수(CSI=0.233)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.051로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.435)가 상담공급지수(CSI=0.367)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.068로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1866,19 +1796,13 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>priority:최우선지원; weak:상담인력부족; matrix:인프라취약</t>
+          <t>priority:최우선지원; weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA12" t="n">
-        <v>34.7735764364937</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>127.860278182481</v>
       </c>
     </row>
     <row r="13">
@@ -1912,7 +1836,7 @@
         <v>0.4</v>
       </c>
       <c r="H13" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I13" t="n">
         <v>0.2006693383532846</v>
@@ -1924,10 +1848,10 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1668897794510948</v>
+        <v>0.1779897794510949</v>
       </c>
       <c r="M13" t="n">
-        <v>0.03355644611776148</v>
+        <v>0.04465644611776159</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1961,7 +1885,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>해당 학교는 상담수요지수(CDI=0.167)가 상담공급지수(CSI=0.133)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.034로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담수요지수(CDI=0.178)가 상담공급지수(CSI=0.133)보다 높아 수요 대비 공급이 상대적으로 부족한 학교로 분류된다. 우선지원점수는 0.045로, 수요가 공급보다 높은 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1993,12 +1917,6 @@
         <is>
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA13" t="n">
-        <v>35.3884618653624</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>128.013066406181</v>
       </c>
     </row>
     <row r="14">
@@ -2114,12 +2032,6 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA14" t="n">
-        <v>35.1186058925822</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>128.488704531696</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2234,12 +2146,6 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA15" t="n">
-        <v>34.8610875931935</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>128.688426101367</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2354,12 +2260,6 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA16" t="n">
-        <v>35.17410570015</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>128.806980454276</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2392,7 +2292,7 @@
         <v>0.4</v>
       </c>
       <c r="H17" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I17" t="n">
         <v>0.0108114159662646</v>
@@ -2404,10 +2304,10 @@
         <v>0.1333333333333333</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1036038053220882</v>
+        <v>0.1147038053220882</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.02972952801124511</v>
+        <v>-0.01862952801124511</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -2441,7 +2341,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.133)가 상담수요지수(CDI=0.104)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.030로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.133)가 상담수요지수(CDI=0.115)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.019로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2473,12 +2373,6 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA17" t="n">
-        <v>35.1981312504391</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>127.927502886143</v>
       </c>
     </row>
     <row r="18">
@@ -2594,12 +2488,6 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA18" t="n">
-        <v>35.0870312998754</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>128.095881932228</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2714,12 +2602,6 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA19" t="n">
-        <v>35.1879210181996</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>128.800517861807</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2834,12 +2716,6 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA20" t="n">
-        <v>35.2020104293439</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>128.803920376232</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2872,7 +2748,7 @@
         <v>1</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I21" t="n">
         <v>0.020796896772864</v>
@@ -2884,10 +2760,10 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2309249201268014</v>
+        <v>0.2531582534601347</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.1024084132065319</v>
+        <v>-0.08017507987319861</v>
       </c>
       <c r="N21" t="inlineStr">
         <is>
@@ -2921,7 +2797,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.231)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.102로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.253)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.080로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2953,23 +2829,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA21" t="n">
-        <v>35.5015485342887</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>128.750923782839</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>480041415</t>
+          <t>480041515</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>웅상고등학교</t>
+          <t>창원성민여자고등학교</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2979,35 +2849,35 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3533756980719273</v>
+        <v>0.0083591781576696</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1186373547998291</v>
+        <v>0.03989642247994184</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L22" t="n">
-        <v>0.4906710176239188</v>
+        <v>0.2383185335458705</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1093289823760812</v>
+        <v>-0.09501479978746283</v>
       </c>
       <c r="N22" t="inlineStr">
         <is>
@@ -3016,17 +2886,17 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3036,27 +2906,27 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.491)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.109로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.238)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.095로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>수요 상위</t>
+          <t>수요 하위</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>공급 중위</t>
+          <t>공급 하위</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>고수요 보완형</t>
+          <t>최소 인프라 보완형</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -3066,30 +2936,24 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>priority:우선지원; matrix:고수요보완; weak:Wee센터접근성낮음</t>
+          <t>priority:우선지원; weak:상담인력부족; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA22" t="n">
-        <v>35.3781486727198</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>129.145038841883</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>480041515</t>
+          <t>480041937</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>창원성민여자고등학교</t>
+          <t>창녕옥야고등학교</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -3099,35 +2963,35 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I23" t="n">
-        <v>0.0083591781576696</v>
+        <v>0.2314199132474892</v>
       </c>
       <c r="J23" t="n">
-        <v>0.03989642247994184</v>
+        <v>0.1838490566037736</v>
       </c>
       <c r="K23" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2160852002125372</v>
+        <v>0.3606563232837542</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1172481331207961</v>
+        <v>-0.1060103433829124</v>
       </c>
       <c r="N23" t="inlineStr">
         <is>
@@ -3141,7 +3005,7 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
@@ -3156,17 +3020,17 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.216)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.117로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.361)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.106로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>수요 하위</t>
+          <t>수요 중위</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
@@ -3176,7 +3040,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>최소 인프라 보완형</t>
+          <t>잠재 취약형</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -3186,30 +3050,24 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>priority:우선지원; weak:상담인력부족; matrix:인프라취약</t>
+          <t>priority:우선지원; weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA23" t="n">
-        <v>35.2588412928716</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>128.615113707806</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>480041175</t>
+          <t>480041415</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>김해가야고등학교</t>
+          <t>웅상고등학교</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -3219,35 +3077,35 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="F24" t="n">
         <v>1</v>
       </c>
       <c r="G24" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="H24" t="n">
         <v>1</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4928247358275297</v>
+        <v>0.3533756980719273</v>
       </c>
       <c r="J24" t="n">
-        <v>0.1490343736403845</v>
+        <v>0.1186373547998291</v>
       </c>
       <c r="K24" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.6</v>
       </c>
       <c r="L24" t="n">
-        <v>0.5472863698226381</v>
+        <v>0.4906710176239188</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.1193802968440285</v>
+        <v>-0.1093289823760812</v>
       </c>
       <c r="N24" t="inlineStr">
         <is>
@@ -3266,7 +3124,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -3276,12 +3134,12 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.547)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.119로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.491)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.109로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3306,30 +3164,24 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>priority:우선지원; matrix:고수요보완; weak:상담인력부족</t>
+          <t>priority:우선지원; matrix:고수요보완; weak:Wee센터접근성낮음</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA24" t="n">
-        <v>35.2362292607702</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>128.871079332959</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>480041460</t>
+          <t>480041612</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>진해고등학교</t>
+          <t>거창고등학교</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -3339,35 +3191,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>거창군</t>
         </is>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I25" t="n">
-        <v>0.2271658647607984</v>
+        <v>0.0011011854958523</v>
       </c>
       <c r="J25" t="n">
-        <v>0.1062570197451786</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="L25" t="n">
-        <v>0.4444742948353257</v>
+        <v>0.2226003951652841</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.122192371831341</v>
+        <v>-0.1107329381680492</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
@@ -3381,12 +3233,12 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3396,27 +3248,27 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.444)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.122로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.223)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.111로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>수요 중위</t>
+          <t>수요 하위</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>공급 중위</t>
+          <t>공급 하위</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>평균 관리형</t>
+          <t>최소 인프라 보완형</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
@@ -3426,30 +3278,24 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>priority:우선지원; weak:상담인력부족</t>
+          <t>priority:우선지원; weak:상담인력부족; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA25" t="n">
-        <v>35.1608116244956</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>128.665178884498</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>480041937</t>
+          <t>480041708</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>창녕옥야고등학교</t>
+          <t>보광고등학교</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -3459,35 +3305,35 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H26" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.5952075874026673</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.1930397432721377</v>
+      </c>
+      <c r="K26" t="n">
         <v>0.6</v>
       </c>
-      <c r="I26" t="n">
-        <v>0.2314199132474892</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0.1838490566037736</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.4666666666666666</v>
-      </c>
       <c r="L26" t="n">
-        <v>0.3384229899504209</v>
+        <v>0.4849824435582684</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1282436767162457</v>
+        <v>-0.1150175564417316</v>
       </c>
       <c r="N26" t="inlineStr">
         <is>
@@ -3496,7 +3342,7 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3506,7 +3352,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -3516,27 +3362,27 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.338)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.128로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.485)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.115로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>수요 중위</t>
+          <t>수요 상위</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>공급 하위</t>
+          <t>공급 중위</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>잠재 취약형</t>
+          <t>고수요 보완형</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
@@ -3546,30 +3392,24 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>priority:우선지원; weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
+          <t>priority:우선지원; matrix:고수요보완; weak:Wee센터접근성낮음</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA26" t="n">
-        <v>35.6002401214951</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>128.381000093523</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>480041520</t>
+          <t>480041175</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>통영여자고등학교</t>
+          <t>김해가야고등학교</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3579,7 +3419,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3595,19 +3435,19 @@
         <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>0.5158423179000511</v>
+        <v>0.4928247358275297</v>
       </c>
       <c r="J27" t="n">
-        <v>0.09815651617954205</v>
+        <v>0.1490343736403845</v>
       </c>
       <c r="K27" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L27" t="n">
-        <v>0.5379996113598644</v>
+        <v>0.5472863698226381</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.1286670553068022</v>
+        <v>-0.1193802968440285</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
@@ -3636,12 +3476,12 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.538)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.129로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.547)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.119로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3673,23 +3513,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA27" t="n">
-        <v>34.8402101668269</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>128.410152174772</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>480041612</t>
+          <t>480041460</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>거창고등학교</t>
+          <t>진해고등학교</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -3699,35 +3533,35 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>거창군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H28" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>0.0011011854958523</v>
+        <v>0.2271658647607984</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>0.1062570197451786</v>
       </c>
       <c r="K28" t="n">
-        <v>0.3333333333333333</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L28" t="n">
-        <v>0.2003670618319507</v>
+        <v>0.4444742948353257</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.1329662715013826</v>
+        <v>-0.122192371831341</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
@@ -3741,12 +3575,12 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3756,27 +3590,27 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee클래스 신설 또는 운영 현황 재확인 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.200)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.133로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.444)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.122로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>수요 하위</t>
+          <t>수요 중위</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>공급 하위</t>
+          <t>공급 중위</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>최소 인프라 보완형</t>
+          <t>평균 관리형</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
@@ -3786,30 +3620,24 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>priority:우선지원; weak:상담인력부족; matrix:인프라취약</t>
+          <t>priority:우선지원; weak:상담인력부족</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA28" t="n">
-        <v>35.6933239305256</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>127.911109160251</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>480041430</t>
+          <t>480041798</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>진양고등학교</t>
+          <t>용남고등학교</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -3819,7 +3647,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>사천시</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3829,25 +3657,25 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H29" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I29" t="n">
-        <v>0.2127050585131158</v>
+        <v>0.3138411838772603</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0772717592246427</v>
+        <v>0.04618335628565808</v>
       </c>
       <c r="K29" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4299922725792529</v>
+        <v>0.3422415133876395</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.1366743940874138</v>
+        <v>-0.1244251532790271</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
@@ -3866,7 +3694,7 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3876,12 +3704,12 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.430)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.137로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.342)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.124로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3891,12 +3719,12 @@
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>공급 중위</t>
+          <t>공급 하위</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>평균 관리형</t>
+          <t>잠재 취약형</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
@@ -3906,30 +3734,24 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>priority:우선지원; weak:상담인력부족</t>
+          <t>priority:우선지원; weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA29" t="n">
-        <v>35.1758160065726</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>128.152119185535</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>480041708</t>
+          <t>480041520</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>보광고등학교</t>
+          <t>통영여자고등학교</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -3939,35 +3761,35 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.7</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
         <v>1</v>
       </c>
       <c r="G30" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H30" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I30" t="n">
-        <v>0.5952075874026673</v>
+        <v>0.5158423179000511</v>
       </c>
       <c r="J30" t="n">
-        <v>0.1930397432721377</v>
+        <v>0.09815651617954205</v>
       </c>
       <c r="K30" t="n">
-        <v>0.6</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L30" t="n">
-        <v>0.462749110224935</v>
+        <v>0.5379996113598644</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.137250889775065</v>
+        <v>-0.1286670553068022</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -3986,7 +3808,7 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3996,12 +3818,12 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.137로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.538)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.129로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -4026,19 +3848,13 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>priority:우선지원; matrix:고수요보완; weak:Wee센터접근성낮음</t>
+          <t>priority:우선지원; matrix:고수요보완; weak:상담인력부족</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA30" t="n">
-        <v>35.4918679846425</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>129.087318690399</v>
       </c>
     </row>
     <row r="31">
@@ -4154,12 +3970,6 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA31" t="n">
-        <v>34.8519719382777</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>128.586799629528</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4274,12 +4084,6 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA32" t="n">
-        <v>34.8540268503364</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>128.424261789301</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4394,22 +4198,16 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA33" t="n">
-        <v>34.8928558087942</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>128.637235165959</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>480041347</t>
+          <t>480041888</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>김해제일고등학교</t>
+          <t>창원남고등학교</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -4419,7 +4217,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4432,22 +4230,22 @@
         <v>1</v>
       </c>
       <c r="H34" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I34" t="n">
-        <v>0.2969432680024733</v>
+        <v>0.7795999680122426</v>
       </c>
       <c r="J34" t="n">
-        <v>0.1478483958194806</v>
+        <v>0.05377528981354961</v>
       </c>
       <c r="K34" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L34" t="n">
-        <v>0.4815972212739846</v>
+        <v>0.5000250859419307</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.1850694453926821</v>
+        <v>-0.1666415807247359</v>
       </c>
       <c r="N34" t="inlineStr">
         <is>
@@ -4476,12 +4274,12 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.482)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.185로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.500)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.167로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4513,23 +4311,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA34" t="n">
-        <v>35.2395584937856</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>128.853839114441</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>480041888</t>
+          <t>480041347</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>창원남고등학교</t>
+          <t>김해제일고등학교</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -4539,7 +4331,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4552,22 +4344,22 @@
         <v>1</v>
       </c>
       <c r="H35" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I35" t="n">
-        <v>0.7795999680122426</v>
+        <v>0.2969432680024733</v>
       </c>
       <c r="J35" t="n">
-        <v>0.05377528981354961</v>
+        <v>0.1478483958194806</v>
       </c>
       <c r="K35" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L35" t="n">
-        <v>0.4777917526085974</v>
+        <v>0.4815972212739846</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.1888749140580692</v>
+        <v>-0.1850694453926821</v>
       </c>
       <c r="N35" t="inlineStr">
         <is>
@@ -4596,12 +4388,12 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.478)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.189로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.482)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.185로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4633,12 +4425,6 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA35" t="n">
-        <v>35.2139715595235</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>128.679749626138</v>
       </c>
     </row>
     <row r="36">
@@ -4754,12 +4540,6 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA36" t="n">
-        <v>35.2122838519552</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>128.582107501894</v>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4874,12 +4654,6 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA37" t="n">
-        <v>35.3486672549866</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>129.044490862753</v>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4994,22 +4768,16 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA38" t="n">
-        <v>35.304767715615</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>128.730004720208</v>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>480041840</t>
+          <t>480041485</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>진해세화여자고등학교</t>
+          <t>창원용호고등학교</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5029,25 +4797,25 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H39" t="n">
         <v>1</v>
       </c>
       <c r="I39" t="n">
-        <v>0.2667806965841105</v>
+        <v>0.4884023438779649</v>
       </c>
       <c r="J39" t="n">
-        <v>0.109802957036652</v>
+        <v>0.1536074441677842</v>
       </c>
       <c r="K39" t="n">
-        <v>0.6999999999999998</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>0.4588612178735875</v>
+        <v>0.5473365960152498</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.2411387821264123</v>
+        <v>-0.2526634039847502</v>
       </c>
       <c r="N39" t="inlineStr">
         <is>
@@ -5076,12 +4844,12 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.459)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.241로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.547)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.253로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -5113,23 +4881,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA39" t="n">
-        <v>35.1614104475708</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>128.69421717403</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>480041485</t>
+          <t>480041478</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>창원용호고등학교</t>
+          <t>창원신월고등학교</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5155,19 +4917,19 @@
         <v>1</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4884023438779649</v>
+        <v>0.4646971034293428</v>
       </c>
       <c r="J40" t="n">
-        <v>0.1536074441677842</v>
+        <v>0.1011385011385011</v>
       </c>
       <c r="K40" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>0.5473365960152498</v>
+        <v>0.5219452015226146</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.2526634039847502</v>
+        <v>-0.2780547984773853</v>
       </c>
       <c r="N40" t="inlineStr">
         <is>
@@ -5196,12 +4958,12 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.547)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.253로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.522)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.278로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -5233,23 +4995,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA40" t="n">
-        <v>35.2340983095277</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>128.676689060939</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>480041478</t>
+          <t>480041440</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>창원신월고등학교</t>
+          <t>진주고등학교</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5259,7 +5015,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -5275,19 +5031,19 @@
         <v>1</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4646971034293428</v>
+        <v>0.4092675560543229</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1011385011385011</v>
+        <v>0.06253203028192925</v>
       </c>
       <c r="K41" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>0.5219452015226146</v>
+        <v>0.490599862112084</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.2780547984773853</v>
+        <v>-0.3094001378879159</v>
       </c>
       <c r="N41" t="inlineStr">
         <is>
@@ -5321,7 +5077,7 @@
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.522)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.278로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.491)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.309로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -5353,23 +5109,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA41" t="n">
-        <v>35.2268377252433</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>128.693671883358</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>480041440</t>
+          <t>480041476</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>진주고등학교</t>
+          <t>창원사파고등학교</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5379,7 +5129,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5395,19 +5145,19 @@
         <v>1</v>
       </c>
       <c r="I42" t="n">
-        <v>0.4092675560543229</v>
+        <v>0.3633825515229166</v>
       </c>
       <c r="J42" t="n">
-        <v>0.06253203028192925</v>
+        <v>0.06537634408602151</v>
       </c>
       <c r="K42" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>0.490599862112084</v>
+        <v>0.4762529652029794</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.3094001378879159</v>
+        <v>-0.3237470347970205</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -5436,12 +5186,12 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토; 실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.491)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.309로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.476)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.324로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -5473,23 +5223,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA42" t="n">
-        <v>35.2000965354561</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>128.080235135137</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>480041476</t>
+          <t>480041177</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>창원사파고등학교</t>
+          <t>김해경원고등학교</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5499,7 +5243,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -5515,19 +5259,19 @@
         <v>1</v>
       </c>
       <c r="I43" t="n">
-        <v>0.3633825515229166</v>
+        <v>0.325164981619064</v>
       </c>
       <c r="J43" t="n">
-        <v>0.06537634408602151</v>
+        <v>0.0933794595346976</v>
       </c>
       <c r="K43" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>0.4762529652029794</v>
+        <v>0.4728481470512538</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.3237470347970205</v>
+        <v>-0.3271518529487462</v>
       </c>
       <c r="N43" t="inlineStr">
         <is>
@@ -5561,7 +5305,7 @@
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.476)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.324로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.473)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.327로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -5593,23 +5337,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA43" t="n">
-        <v>35.2215869552647</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>128.704540418351</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>480041177</t>
+          <t>480041946</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>김해경원고등학교</t>
+          <t>거제상문고등학교</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5619,7 +5357,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>거제시</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -5635,19 +5373,19 @@
         <v>1</v>
       </c>
       <c r="I44" t="n">
-        <v>0.325164981619064</v>
+        <v>0.3326468748350401</v>
       </c>
       <c r="J44" t="n">
-        <v>0.0933794595346976</v>
+        <v>0.07464120483687738</v>
       </c>
       <c r="K44" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>0.4728481470512538</v>
+        <v>0.4690960265573058</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.3271518529487462</v>
+        <v>-0.3309039734426941</v>
       </c>
       <c r="N44" t="inlineStr">
         <is>
@@ -5681,7 +5419,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.473)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.327로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.469)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.331로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5713,23 +5451,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA44" t="n">
-        <v>35.2318563706783</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>128.861817165997</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>480041946</t>
+          <t>480041704</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>거제상문고등학교</t>
+          <t>마산무학여자고등학교</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5739,7 +5471,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>거제시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -5755,19 +5487,19 @@
         <v>1</v>
       </c>
       <c r="I45" t="n">
-        <v>0.3326468748350401</v>
+        <v>0.3585012688069095</v>
       </c>
       <c r="J45" t="n">
-        <v>0.07464120483687738</v>
+        <v>0.04616358873301335</v>
       </c>
       <c r="K45" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>0.4690960265573058</v>
+        <v>0.4682216191799743</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.3309039734426941</v>
+        <v>-0.3317783808200256</v>
       </c>
       <c r="N45" t="inlineStr">
         <is>
@@ -5801,7 +5533,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.469)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.331로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.468)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.332로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5833,23 +5565,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA45" t="n">
-        <v>34.8633930399088</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>128.646715350706</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>480041704</t>
+          <t>480041560</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>마산무학여자고등학교</t>
+          <t>합포고등학교</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5875,19 +5601,19 @@
         <v>1</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3585012688069095</v>
+        <v>0.3186340225512735</v>
       </c>
       <c r="J46" t="n">
-        <v>0.04616358873301335</v>
+        <v>0.07371730382293762</v>
       </c>
       <c r="K46" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>0.4682216191799743</v>
+        <v>0.4641171087914038</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.3317783808200256</v>
+        <v>-0.3358828912085962</v>
       </c>
       <c r="N46" t="inlineStr">
         <is>
@@ -5921,7 +5647,7 @@
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.468)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.332로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.464)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.336로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5953,23 +5679,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA46" t="n">
-        <v>35.2229995202771</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>128.574977671659</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>480041560</t>
+          <t>480041936</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>합포고등학교</t>
+          <t>물금고등학교</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5979,7 +5699,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5995,19 +5715,19 @@
         <v>1</v>
       </c>
       <c r="I47" t="n">
-        <v>0.3186340225512735</v>
+        <v>0.2848459134604937</v>
       </c>
       <c r="J47" t="n">
-        <v>0.07371730382293762</v>
+        <v>0.1047625000482329</v>
       </c>
       <c r="K47" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>0.4641171087914038</v>
+        <v>0.4632028045029088</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.3358828912085962</v>
+        <v>-0.3367971954970911</v>
       </c>
       <c r="N47" t="inlineStr">
         <is>
@@ -6041,7 +5761,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.464)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.336로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -6073,23 +5793,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA47" t="n">
-        <v>35.2094121899909</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>128.5643385877</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>480041936</t>
+          <t>480041325</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>물금고등학교</t>
+          <t>진주중앙고등학교</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -6099,7 +5813,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -6115,19 +5829,19 @@
         <v>1</v>
       </c>
       <c r="I48" t="n">
-        <v>0.2848459134604937</v>
+        <v>0.3059509962586563</v>
       </c>
       <c r="J48" t="n">
-        <v>0.1047625000482329</v>
+        <v>0.08280695283323346</v>
       </c>
       <c r="K48" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>0.4632028045029088</v>
+        <v>0.4629193163639632</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.3367971954970911</v>
+        <v>-0.3370806836360367</v>
       </c>
       <c r="N48" t="inlineStr">
         <is>
@@ -6193,23 +5907,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA48" t="n">
-        <v>35.3356821070533</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>129.01633749355</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>480041325</t>
+          <t>480041490</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>진주중앙고등학교</t>
+          <t>창원중앙고등학교</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -6219,7 +5927,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -6235,19 +5943,19 @@
         <v>1</v>
       </c>
       <c r="I49" t="n">
-        <v>0.3059509962586563</v>
+        <v>0.3076451994709415</v>
       </c>
       <c r="J49" t="n">
-        <v>0.08280695283323346</v>
+        <v>0.08042049605698119</v>
       </c>
       <c r="K49" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>0.4629193163639632</v>
+        <v>0.4626885651759742</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.3370806836360367</v>
+        <v>-0.3373114348240258</v>
       </c>
       <c r="N49" t="inlineStr">
         <is>
@@ -6313,23 +6021,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA49" t="n">
-        <v>35.1940098560428</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>128.119014158396</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>480041490</t>
+          <t>480041450</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>창원중앙고등학교</t>
+          <t>진주여자고등학교</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -6339,7 +6041,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -6355,19 +6057,19 @@
         <v>1</v>
       </c>
       <c r="I50" t="n">
-        <v>0.3076451994709415</v>
+        <v>0.291193675268403</v>
       </c>
       <c r="J50" t="n">
-        <v>0.08042049605698119</v>
+        <v>0.09369861612509398</v>
       </c>
       <c r="K50" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>0.4626885651759742</v>
+        <v>0.4616307637978323</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.3373114348240258</v>
+        <v>-0.3383692362021676</v>
       </c>
       <c r="N50" t="inlineStr">
         <is>
@@ -6401,7 +6103,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.463)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.462)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.338로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -6433,23 +6135,17 @@
         <is>
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA50" t="n">
-        <v>35.2318634188245</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>128.677999454169</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>480041450</t>
+          <t>480041608</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>진주여자고등학교</t>
+          <t>대성일고등학교</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -6459,11 +6155,11 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>거창군</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F51" t="n">
         <v>1</v>
@@ -6472,31 +6168,31 @@
         <v>1</v>
       </c>
       <c r="H51" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I51" t="n">
-        <v>0.291193675268403</v>
+        <v>0.4817851398830783</v>
       </c>
       <c r="J51" t="n">
-        <v>0.09369861612509398</v>
+        <v>0.2339320004518243</v>
       </c>
       <c r="K51" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L51" t="n">
-        <v>0.4616307637978323</v>
+        <v>0.4608057134449675</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.3383692362021676</v>
+        <v>-0.4391942865550325</v>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>모니터링</t>
+          <t>안정</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 높음</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6516,12 +6212,12 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.462)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.338로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.461)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.439로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -6531,45 +6227,39 @@
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>공급 중위</t>
+          <t>공급 상위</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>고수요 보완형</t>
+          <t>고수요 유지관리형</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>우선 보완형</t>
+          <t>고수요 유지관리형</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>matrix:고수요보완</t>
+          <t>matrix:고수요유지</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
-        </is>
-      </c>
-      <c r="AA51" t="n">
-        <v>35.2011484686855</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>128.076771617458</v>
+          <t>상담수요가 높지만 공급도 비교적 확보되어 있어 기존 인프라 유지와 프로그램 질 관리가 필요한 유형</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>480041684</t>
+          <t>480041891</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>마산제일여자고등학교</t>
+          <t>창원대산고등학교</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -6589,25 +6279,25 @@
         <v>1</v>
       </c>
       <c r="G52" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H52" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I52" t="n">
-        <v>0.2113677737788978</v>
+        <v>0.2149093505434027</v>
       </c>
       <c r="J52" t="n">
-        <v>0.06897355576600861</v>
+        <v>0.1225239661720482</v>
       </c>
       <c r="K52" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.4666666666666666</v>
       </c>
       <c r="L52" t="n">
-        <v>0.4267804431816355</v>
+        <v>0.3347111055718169</v>
       </c>
       <c r="M52" t="n">
-        <v>-0.1398862234850312</v>
+        <v>-0.1319555610948497</v>
       </c>
       <c r="N52" t="inlineStr">
         <is>
@@ -6626,22 +6316,22 @@
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>수요-공급 불균형 우선 개선</t>
+          <t>권역별 순회상담 또는 최소 인프라 보완</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.427)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.140로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.335)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.132로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -6651,12 +6341,12 @@
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>공급 중위</t>
+          <t>공급 하위</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>평균 관리형</t>
+          <t>잠재 취약형</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
@@ -6666,30 +6356,24 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>weak:상담인력부족</t>
+          <t>weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA52" t="n">
-        <v>35.1886431182834</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>128.556414445409</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>480041798</t>
+          <t>480041430</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>용남고등학교</t>
+          <t>진양고등학교</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -6699,7 +6383,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>사천시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6709,25 +6393,25 @@
         <v>1</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H53" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I53" t="n">
-        <v>0.3138411838772603</v>
+        <v>0.2127050585131158</v>
       </c>
       <c r="J53" t="n">
-        <v>0.04618335628565808</v>
+        <v>0.0772717592246427</v>
       </c>
       <c r="K53" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L53" t="n">
-        <v>0.3200081800543061</v>
+        <v>0.4299922725792529</v>
       </c>
       <c r="M53" t="n">
-        <v>-0.1466584866123605</v>
+        <v>-0.1366743940874138</v>
       </c>
       <c r="N53" t="inlineStr">
         <is>
@@ -6746,22 +6430,22 @@
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>수요-공급 불균형 우선 개선</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.320)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.147로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.430)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.137로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6771,12 +6455,12 @@
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>공급 하위</t>
+          <t>공급 중위</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>잠재 취약형</t>
+          <t>평균 관리형</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -6786,30 +6470,24 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
+          <t>weak:상담인력부족</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA53" t="n">
-        <v>35.0440465325682</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>128.063654425894</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>480041891</t>
+          <t>480041684</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>창원대산고등학교</t>
+          <t>마산제일여자고등학교</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -6829,25 +6507,25 @@
         <v>1</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>0.2149093505434027</v>
+        <v>0.2113677737788978</v>
       </c>
       <c r="J54" t="n">
-        <v>0.1225239661720482</v>
+        <v>0.06897355576600861</v>
       </c>
       <c r="K54" t="n">
-        <v>0.4666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L54" t="n">
-        <v>0.3124777722384836</v>
+        <v>0.4267804431816355</v>
       </c>
       <c r="M54" t="n">
-        <v>-0.154188894428183</v>
+        <v>-0.1398862234850312</v>
       </c>
       <c r="N54" t="inlineStr">
         <is>
@@ -6866,22 +6544,22 @@
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>수요-공급 불균형 우선 개선</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.312)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.154로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.427)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.140로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6891,12 +6569,12 @@
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>공급 하위</t>
+          <t>공급 중위</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>잠재 취약형</t>
+          <t>평균 관리형</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -6906,19 +6584,13 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>weak:상담인력부족; weak:Wee센터접근성낮음; matrix:인프라취약</t>
+          <t>weak:상담인력부족</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA54" t="n">
-        <v>35.3333445855717</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>128.710347424496</v>
       </c>
     </row>
     <row r="55">
@@ -6952,7 +6624,7 @@
         <v>1</v>
       </c>
       <c r="H55" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
@@ -6964,10 +6636,10 @@
         <v>0.3333333333333333</v>
       </c>
       <c r="L55" t="n">
-        <v>0.1340136054421769</v>
+        <v>0.1451136054421769</v>
       </c>
       <c r="M55" t="n">
-        <v>-0.1993197278911564</v>
+        <v>-0.1882197278911564</v>
       </c>
       <c r="N55" t="inlineStr">
         <is>
@@ -7001,7 +6673,7 @@
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.134)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.199로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.333)가 상담수요지수(CDI=0.145)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.188로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee클래스 미운영이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -7033,12 +6705,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA55" t="n">
-        <v>35.3241617419833</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>128.24536466054</v>
       </c>
     </row>
     <row r="56">
@@ -7072,7 +6738,7 @@
         <v>0.4</v>
       </c>
       <c r="H56" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I56" t="n">
         <v>0.4096972760817491</v>
@@ -7084,10 +6750,10 @@
         <v>0.4666666666666666</v>
       </c>
       <c r="L56" t="n">
-        <v>0.2657045146747776</v>
+        <v>0.2768045146747776</v>
       </c>
       <c r="M56" t="n">
-        <v>-0.200962151991889</v>
+        <v>-0.189862151991889</v>
       </c>
       <c r="N56" t="inlineStr">
         <is>
@@ -7121,7 +6787,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.266)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.201로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.277)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.190로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -7153,12 +6819,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA56" t="n">
-        <v>35.3727006487523</v>
-      </c>
-      <c r="AB56" t="n">
-        <v>128.713458715223</v>
       </c>
     </row>
     <row r="57">
@@ -7192,7 +6852,7 @@
         <v>0.4</v>
       </c>
       <c r="H57" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I57" t="n">
         <v>0.4205334769382167</v>
@@ -7204,10 +6864,10 @@
         <v>0.4666666666666666</v>
       </c>
       <c r="L57" t="n">
-        <v>0.2642742111882409</v>
+        <v>0.2753742111882409</v>
       </c>
       <c r="M57" t="n">
-        <v>-0.2023924554784257</v>
+        <v>-0.1912924554784257</v>
       </c>
       <c r="N57" t="inlineStr">
         <is>
@@ -7241,7 +6901,7 @@
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.264)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.202로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.275)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.191로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -7273,12 +6933,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA57" t="n">
-        <v>34.8574955201497</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>128.012231826952</v>
       </c>
     </row>
     <row r="58">
@@ -7312,7 +6966,7 @@
         <v>0.4</v>
       </c>
       <c r="H58" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I58" t="n">
         <v>0.3357113788902203</v>
@@ -7324,10 +6978,10 @@
         <v>0.4666666666666666</v>
       </c>
       <c r="L58" t="n">
-        <v>0.2605137326923958</v>
+        <v>0.2716137326923958</v>
       </c>
       <c r="M58" t="n">
-        <v>-0.2061529339742708</v>
+        <v>-0.1950529339742708</v>
       </c>
       <c r="N58" t="inlineStr">
         <is>
@@ -7361,7 +7015,7 @@
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.261)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.206로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.272)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.195로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -7393,12 +7047,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA58" t="n">
-        <v>35.4010686823669</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>128.842859941817</v>
       </c>
     </row>
     <row r="59">
@@ -7432,7 +7080,7 @@
         <v>0.4</v>
       </c>
       <c r="H59" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I59" t="n">
         <v>0.4787365767333901</v>
@@ -7444,10 +7092,10 @@
         <v>0.4666666666666666</v>
       </c>
       <c r="L59" t="n">
-        <v>0.25957885891113</v>
+        <v>0.27067885891113</v>
       </c>
       <c r="M59" t="n">
-        <v>-0.2070878077555366</v>
+        <v>-0.1959878077555366</v>
       </c>
       <c r="N59" t="inlineStr">
         <is>
@@ -7481,7 +7129,7 @@
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.260)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.207로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.271)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.196로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -7513,12 +7161,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA59" t="n">
-        <v>35.306322889172</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>127.964302293712</v>
       </c>
     </row>
     <row r="60">
@@ -7634,12 +7276,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA60" t="n">
-        <v>35.1906552527563</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>128.114310474051</v>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7754,12 +7390,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA61" t="n">
-        <v>35.2545664657582</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>128.648822472683</v>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7874,12 +7504,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA62" t="n">
-        <v>35.251846702575</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>128.648926140934</v>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7994,12 +7618,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA63" t="n">
-        <v>34.9141619755733</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>128.646381185422</v>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -8114,12 +7732,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA64" t="n">
-        <v>35.2654778374898</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>128.874553443759</v>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -8234,12 +7846,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA65" t="n">
-        <v>35.2666238467743</v>
-      </c>
-      <c r="AB65" t="n">
-        <v>128.873868698114</v>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -8354,12 +7960,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA66" t="n">
-        <v>35.2157198462691</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>128.114396937049</v>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8474,12 +8074,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA67" t="n">
-        <v>35.2257745182989</v>
-      </c>
-      <c r="AB67" t="n">
-        <v>128.703639766126</v>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8594,12 +8188,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA68" t="n">
-        <v>35.2313933541974</v>
-      </c>
-      <c r="AB68" t="n">
-        <v>128.896080879658</v>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8714,12 +8302,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA69" t="n">
-        <v>35.1959383430221</v>
-      </c>
-      <c r="AB69" t="n">
-        <v>128.561409708496</v>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8834,12 +8416,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA70" t="n">
-        <v>35.3445559166984</v>
-      </c>
-      <c r="AB70" t="n">
-        <v>129.025086059702</v>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8954,12 +8530,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA71" t="n">
-        <v>35.2546883556411</v>
-      </c>
-      <c r="AB71" t="n">
-        <v>128.905474404717</v>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -9074,12 +8644,6 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA72" t="n">
-        <v>35.2034768863412</v>
-      </c>
-      <c r="AB72" t="n">
-        <v>128.700299729442</v>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -9112,7 +8676,7 @@
         <v>0.7</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I73" t="n">
         <v>0.4940415218194545</v>
@@ -9124,10 +8688,10 @@
         <v>0.5666666666666667</v>
       </c>
       <c r="L73" t="n">
-        <v>0.2779255403857343</v>
+        <v>0.2890255403857342</v>
       </c>
       <c r="M73" t="n">
-        <v>-0.2887411262809323</v>
+        <v>-0.2776411262809325</v>
       </c>
       <c r="N73" t="inlineStr">
         <is>
@@ -9161,7 +8725,7 @@
       </c>
       <c r="T73" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.278)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.289로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.289)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.278로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U73" t="inlineStr">
@@ -9193,23 +8757,17 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA73" t="n">
-        <v>35.259597572054</v>
-      </c>
-      <c r="AB73" t="n">
-        <v>128.343533507993</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>480041870</t>
+          <t>480041645</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>창신고등학교</t>
+          <t>김해중앙여자고등학교</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -9219,7 +8777,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -9232,22 +8790,22 @@
         <v>1</v>
       </c>
       <c r="H74" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I74" t="n">
-        <v>0.0364645107070795</v>
+        <v>0.3871806223139501</v>
       </c>
       <c r="J74" t="n">
-        <v>0.06971291371247043</v>
+        <v>0.1075804776739356</v>
       </c>
       <c r="K74" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L74" t="n">
-        <v>0.36872580813985</v>
+        <v>0.3871536999959619</v>
       </c>
       <c r="M74" t="n">
-        <v>-0.2979408585268166</v>
+        <v>-0.2795129666707047</v>
       </c>
       <c r="N74" t="inlineStr">
         <is>
@@ -9266,22 +8824,22 @@
       </c>
       <c r="Q74" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T74" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.369)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.298로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.387)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.280로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U74" t="inlineStr">
@@ -9313,23 +8871,17 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA74" t="n">
-        <v>35.2259412027856</v>
-      </c>
-      <c r="AB74" t="n">
-        <v>128.597554549774</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>480041645</t>
+          <t>480041547</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>김해중앙여자고등학교</t>
+          <t>함안고등학교</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -9339,7 +8891,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>함안군</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -9352,22 +8904,22 @@
         <v>1</v>
       </c>
       <c r="H75" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I75" t="n">
-        <v>0.3871806223139501</v>
+        <v>0.3375120411071955</v>
       </c>
       <c r="J75" t="n">
-        <v>0.1075804776739356</v>
+        <v>0.1446991957387437</v>
       </c>
       <c r="K75" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L75" t="n">
-        <v>0.3649203666626286</v>
+        <v>0.3829704122819798</v>
       </c>
       <c r="M75" t="n">
-        <v>-0.301746300004038</v>
+        <v>-0.2836962543846868</v>
       </c>
       <c r="N75" t="inlineStr">
         <is>
@@ -9386,22 +8938,22 @@
       </c>
       <c r="Q75" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R75" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T75" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.365)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.302로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.383)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.284로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U75" t="inlineStr">
@@ -9433,23 +8985,17 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA75" t="n">
-        <v>35.2322435712973</v>
-      </c>
-      <c r="AB75" t="n">
-        <v>128.887298986012</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>480041547</t>
+          <t>480041870</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>함안고등학교</t>
+          <t>창신고등학교</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -9459,7 +9005,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>함안군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -9472,22 +9018,22 @@
         <v>1</v>
       </c>
       <c r="H76" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I76" t="n">
-        <v>0.3375120411071955</v>
+        <v>0.0364645107070795</v>
       </c>
       <c r="J76" t="n">
-        <v>0.1446991957387437</v>
+        <v>0.06971291371247043</v>
       </c>
       <c r="K76" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L76" t="n">
-        <v>0.3607370789486464</v>
+        <v>0.36872580813985</v>
       </c>
       <c r="M76" t="n">
-        <v>-0.3059295877180203</v>
+        <v>-0.2979408585268166</v>
       </c>
       <c r="N76" t="inlineStr">
         <is>
@@ -9516,12 +9062,12 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T76" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.361)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.306로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.369)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.298로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U76" t="inlineStr">
@@ -9553,12 +9099,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA76" t="n">
-        <v>35.2821326818366</v>
-      </c>
-      <c r="AB76" t="n">
-        <v>128.403305145623</v>
       </c>
     </row>
     <row r="77">
@@ -9592,7 +9132,7 @@
         <v>1</v>
       </c>
       <c r="H77" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I77" t="n">
         <v>0.3527345051160103</v>
@@ -9604,10 +9144,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L77" t="n">
-        <v>0.3425045339844229</v>
+        <v>0.3647378673177562</v>
       </c>
       <c r="M77" t="n">
-        <v>-0.3241621326822438</v>
+        <v>-0.3019287993489104</v>
       </c>
       <c r="N77" t="inlineStr">
         <is>
@@ -9641,7 +9181,7 @@
       </c>
       <c r="T77" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.343)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.324로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.365)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.302로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U77" t="inlineStr">
@@ -9673,12 +9213,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA77" t="n">
-        <v>35.2470659533563</v>
-      </c>
-      <c r="AB77" t="n">
-        <v>128.596987424283</v>
       </c>
     </row>
     <row r="78">
@@ -9712,7 +9246,7 @@
         <v>1</v>
       </c>
       <c r="H78" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I78" t="n">
         <v>0.3886228313634106</v>
@@ -9724,10 +9258,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L78" t="n">
-        <v>0.3418108824381103</v>
+        <v>0.3640442157714436</v>
       </c>
       <c r="M78" t="n">
-        <v>-0.3248557842285563</v>
+        <v>-0.302622450895223</v>
       </c>
       <c r="N78" t="inlineStr">
         <is>
@@ -9761,7 +9295,7 @@
       </c>
       <c r="T78" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.342)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.325로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.364)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.303로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U78" t="inlineStr">
@@ -9793,12 +9327,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA78" t="n">
-        <v>34.9397418584784</v>
-      </c>
-      <c r="AB78" t="n">
-        <v>128.089862085081</v>
       </c>
     </row>
     <row r="79">
@@ -9832,7 +9360,7 @@
         <v>1</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I79" t="n">
         <v>0.3410131426255853</v>
@@ -9844,10 +9372,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L79" t="n">
-        <v>0.341111141986838</v>
+        <v>0.3633444753201713</v>
       </c>
       <c r="M79" t="n">
-        <v>-0.3255555246798286</v>
+        <v>-0.3033221913464954</v>
       </c>
       <c r="N79" t="inlineStr">
         <is>
@@ -9881,7 +9409,7 @@
       </c>
       <c r="T79" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.341)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.326로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.363)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.303로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U79" t="inlineStr">
@@ -9913,12 +9441,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA79" t="n">
-        <v>35.2273146732954</v>
-      </c>
-      <c r="AB79" t="n">
-        <v>128.66248611227</v>
       </c>
     </row>
     <row r="80">
@@ -9952,7 +9474,7 @@
         <v>1</v>
       </c>
       <c r="H80" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I80" t="n">
         <v>0.3042280023489025</v>
@@ -9964,10 +9486,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L80" t="n">
-        <v>0.3358683028889951</v>
+        <v>0.3581016362223284</v>
       </c>
       <c r="M80" t="n">
-        <v>-0.3307983637776715</v>
+        <v>-0.3085650304443383</v>
       </c>
       <c r="N80" t="inlineStr">
         <is>
@@ -10001,7 +9523,7 @@
       </c>
       <c r="T80" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.336)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.331로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.358)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.309로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U80" t="inlineStr">
@@ -10033,12 +9555,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA80" t="n">
-        <v>35.2382686393143</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>128.852720108492</v>
       </c>
     </row>
     <row r="81">
@@ -10072,7 +9588,7 @@
         <v>1</v>
       </c>
       <c r="H81" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I81" t="n">
         <v>0.2624588353774778</v>
@@ -10084,10 +9600,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L81" t="n">
-        <v>0.3330618545699436</v>
+        <v>0.355295187903277</v>
       </c>
       <c r="M81" t="n">
-        <v>-0.333604812096723</v>
+        <v>-0.3113714787633896</v>
       </c>
       <c r="N81" t="inlineStr">
         <is>
@@ -10121,7 +9637,7 @@
       </c>
       <c r="T81" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.333)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.334로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.355)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.311로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U81" t="inlineStr">
@@ -10153,23 +9669,17 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA81" t="n">
-        <v>34.8392638643409</v>
-      </c>
-      <c r="AB81" t="n">
-        <v>127.902439949009</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>480041710</t>
+          <t>480041876</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>영산고등학교</t>
+          <t>창원경일고등학교</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -10179,7 +9689,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>창녕군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E82" t="n">
@@ -10189,25 +9699,25 @@
         <v>1</v>
       </c>
       <c r="G82" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3</v>
+        <v>0.6667</v>
       </c>
       <c r="I82" t="n">
-        <v>0.2296776803799888</v>
+        <v>0.295967901342231</v>
       </c>
       <c r="J82" t="n">
-        <v>0.1263094278807413</v>
+        <v>0.0411237298266587</v>
       </c>
       <c r="K82" t="n">
-        <v>0.5666666666666667</v>
+        <v>0.6666666666666666</v>
       </c>
       <c r="L82" t="n">
-        <v>0.2186623694202433</v>
+        <v>0.3345972103896299</v>
       </c>
       <c r="M82" t="n">
-        <v>-0.3480042972464233</v>
+        <v>-0.3320694562770367</v>
       </c>
       <c r="N82" t="inlineStr">
         <is>
@@ -10216,37 +9726,37 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q82" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R82" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
         </is>
       </c>
       <c r="T82" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.219)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.348로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.335)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.332로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U82" t="inlineStr">
         <is>
-          <t>수요 하위</t>
+          <t>수요 중위</t>
         </is>
       </c>
       <c r="V82" t="inlineStr">
@@ -10256,7 +9766,7 @@
       </c>
       <c r="W82" t="inlineStr">
         <is>
-          <t>안정 모니터링형</t>
+          <t>평균 관리형</t>
         </is>
       </c>
       <c r="X82" t="inlineStr">
@@ -10273,23 +9783,17 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA82" t="n">
-        <v>35.459602481463</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>128.528366135718</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>480041876</t>
+          <t>480041768</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>창원경일고등학교</t>
+          <t>세종고등학교</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -10299,7 +9803,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -10312,22 +9816,22 @@
         <v>1</v>
       </c>
       <c r="H83" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I83" t="n">
-        <v>0.295967901342231</v>
+        <v>0.2655110230628451</v>
       </c>
       <c r="J83" t="n">
-        <v>0.0411237298266587</v>
+        <v>0.0682096711781313</v>
       </c>
       <c r="K83" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L83" t="n">
-        <v>0.3123638770562966</v>
+        <v>0.3334735647469921</v>
       </c>
       <c r="M83" t="n">
-        <v>-0.35430278961037</v>
+        <v>-0.3331931019196746</v>
       </c>
       <c r="N83" t="inlineStr">
         <is>
@@ -10361,7 +9865,7 @@
       </c>
       <c r="T83" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.312)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.354로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.333)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.333로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U83" t="inlineStr">
@@ -10393,23 +9897,17 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA83" t="n">
-        <v>35.2265865699855</v>
-      </c>
-      <c r="AB83" t="n">
-        <v>128.661213359055</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>480041768</t>
+          <t>480041550</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>세종고등학교</t>
+          <t>함양고등학교</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -10419,7 +9917,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>함양군</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -10432,22 +9930,22 @@
         <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2655110230628451</v>
+        <v>0.215535457316114</v>
       </c>
       <c r="J84" t="n">
-        <v>0.0682096711781313</v>
+        <v>0.1129521918002553</v>
       </c>
       <c r="K84" t="n">
         <v>0.6666666666666666</v>
       </c>
       <c r="L84" t="n">
-        <v>0.3112402314136588</v>
+        <v>0.3317292163721231</v>
       </c>
       <c r="M84" t="n">
-        <v>-0.3554264352530078</v>
+        <v>-0.3349374502945435</v>
       </c>
       <c r="N84" t="inlineStr">
         <is>
@@ -10481,7 +9979,7 @@
       </c>
       <c r="T84" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.311)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.355로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.332)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.335로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U84" t="inlineStr">
@@ -10513,23 +10011,17 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA84" t="n">
-        <v>35.4737805380356</v>
-      </c>
-      <c r="AB84" t="n">
-        <v>128.76371249178</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>480041550</t>
+          <t>480041710</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>함양고등학교</t>
+          <t>영산고등학교</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -10539,7 +10031,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>함양군</t>
+          <t>창녕군</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -10549,25 +10041,25 @@
         <v>1</v>
       </c>
       <c r="G85" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H85" t="n">
-        <v>0.6</v>
+        <v>0.3333</v>
       </c>
       <c r="I85" t="n">
-        <v>0.215535457316114</v>
+        <v>0.2296776803799888</v>
       </c>
       <c r="J85" t="n">
-        <v>0.1129521918002553</v>
+        <v>0.1263094278807413</v>
       </c>
       <c r="K85" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.5666666666666667</v>
       </c>
       <c r="L85" t="n">
-        <v>0.3094958830387898</v>
+        <v>0.2297623694202434</v>
       </c>
       <c r="M85" t="n">
-        <v>-0.3571707836278769</v>
+        <v>-0.3369042972464232</v>
       </c>
       <c r="N85" t="inlineStr">
         <is>
@@ -10576,37 +10068,37 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>권역별 순회상담 또는 최소 인프라 보완</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>전문상담교사 배치 또는 순회상담교사 연계 검토</t>
+          <t>전문상담교사 배치 또는 순회상담교사 연계 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.309)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.357로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.567)가 상담수요지수(CDI=0.230)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.337로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U85" t="inlineStr">
         <is>
-          <t>수요 중위</t>
+          <t>수요 하위</t>
         </is>
       </c>
       <c r="V85" t="inlineStr">
@@ -10616,7 +10108,7 @@
       </c>
       <c r="W85" t="inlineStr">
         <is>
-          <t>평균 관리형</t>
+          <t>안정 모니터링형</t>
         </is>
       </c>
       <c r="X85" t="inlineStr">
@@ -10633,12 +10125,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA85" t="n">
-        <v>35.5136475114705</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>127.721098981375</v>
       </c>
     </row>
     <row r="86">
@@ -10672,7 +10158,7 @@
         <v>1</v>
       </c>
       <c r="H86" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I86" t="n">
         <v>0.3182541452104335</v>
@@ -10684,10 +10170,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L86" t="n">
-        <v>0.3060847150701445</v>
+        <v>0.3283180484034778</v>
       </c>
       <c r="M86" t="n">
-        <v>-0.3605819515965221</v>
+        <v>-0.3383486182631888</v>
       </c>
       <c r="N86" t="inlineStr">
         <is>
@@ -10721,7 +10207,7 @@
       </c>
       <c r="T86" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.306)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.361로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.328)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.338로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U86" t="inlineStr">
@@ -10753,12 +10239,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA86" t="n">
-        <v>35.4952119282651</v>
-      </c>
-      <c r="AB86" t="n">
-        <v>128.75593452466</v>
       </c>
     </row>
     <row r="87">
@@ -10792,7 +10272,7 @@
         <v>1</v>
       </c>
       <c r="H87" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I87" t="n">
         <v>0.1958431664988423</v>
@@ -10804,10 +10284,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L87" t="n">
-        <v>0.305396186848636</v>
+        <v>0.3276295201819693</v>
       </c>
       <c r="M87" t="n">
-        <v>-0.3612704798180306</v>
+        <v>-0.3390371464846973</v>
       </c>
       <c r="N87" t="inlineStr">
         <is>
@@ -10841,7 +10321,7 @@
       </c>
       <c r="T87" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.305)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.361로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.328)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.339로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U87" t="inlineStr">
@@ -10873,12 +10353,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA87" t="n">
-        <v>35.1589968041779</v>
-      </c>
-      <c r="AB87" t="n">
-        <v>128.096534774487</v>
       </c>
     </row>
     <row r="88">
@@ -10912,7 +10386,7 @@
         <v>1</v>
       </c>
       <c r="H88" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I88" t="n">
         <v>0.261803616952978</v>
@@ -10924,10 +10398,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L88" t="n">
-        <v>0.3021932454519877</v>
+        <v>0.324426578785321</v>
       </c>
       <c r="M88" t="n">
-        <v>-0.3644734212146789</v>
+        <v>-0.3422400878813456</v>
       </c>
       <c r="N88" t="inlineStr">
         <is>
@@ -10961,7 +10435,7 @@
       </c>
       <c r="T88" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.302)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.364로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.324)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.342로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U88" t="inlineStr">
@@ -10993,12 +10467,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA88" t="n">
-        <v>34.9678060865735</v>
-      </c>
-      <c r="AB88" t="n">
-        <v>128.318571463973</v>
       </c>
     </row>
     <row r="89">
@@ -11032,7 +10500,7 @@
         <v>1</v>
       </c>
       <c r="H89" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I89" t="n">
         <v>0.1720348935371041</v>
@@ -11044,10 +10512,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L89" t="n">
-        <v>0.3016455595637816</v>
+        <v>0.323878892897115</v>
       </c>
       <c r="M89" t="n">
-        <v>-0.365021107102885</v>
+        <v>-0.3427877737695516</v>
       </c>
       <c r="N89" t="inlineStr">
         <is>
@@ -11081,7 +10549,7 @@
       </c>
       <c r="T89" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.302)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.365로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.324)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.343로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U89" t="inlineStr">
@@ -11113,12 +10581,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA89" t="n">
-        <v>35.2356856577499</v>
-      </c>
-      <c r="AB89" t="n">
-        <v>128.660267954484</v>
       </c>
     </row>
     <row r="90">
@@ -11152,7 +10614,7 @@
         <v>1</v>
       </c>
       <c r="H90" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I90" t="n">
         <v>0.1751204810202206</v>
@@ -11164,10 +10626,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L90" t="n">
-        <v>0.2843825306967742</v>
+        <v>0.3066158640301075</v>
       </c>
       <c r="M90" t="n">
-        <v>-0.3822841359698924</v>
+        <v>-0.3600508026365591</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
@@ -11181,7 +10643,7 @@
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q90" t="inlineStr">
@@ -11201,7 +10663,7 @@
       </c>
       <c r="T90" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.284)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.382로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.307)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.360로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U90" t="inlineStr">
@@ -11233,12 +10695,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA90" t="n">
-        <v>35.1919473175706</v>
-      </c>
-      <c r="AB90" t="n">
-        <v>128.558406311794</v>
       </c>
     </row>
     <row r="91">
@@ -11272,7 +10728,7 @@
         <v>1</v>
       </c>
       <c r="H91" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I91" t="n">
         <v>0.4069727319013836</v>
@@ -11284,10 +10740,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L91" t="n">
-        <v>0.2772013626190284</v>
+        <v>0.2883013626190284</v>
       </c>
       <c r="M91" t="n">
-        <v>-0.3894653040476382</v>
+        <v>-0.3783653040476382</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
@@ -11321,7 +10777,7 @@
       </c>
       <c r="T91" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.277)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.389로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.288)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.378로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U91" t="inlineStr">
@@ -11353,12 +10809,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA91" t="n">
-        <v>35.0639132899941</v>
-      </c>
-      <c r="AB91" t="n">
-        <v>127.746167522591</v>
       </c>
     </row>
     <row r="92">
@@ -11392,7 +10842,7 @@
         <v>1</v>
       </c>
       <c r="H92" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I92" t="n">
         <v>0.4471977650045322</v>
@@ -11404,14 +10854,14 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L92" t="n">
-        <v>0.2604944930967488</v>
+        <v>0.2715944930967488</v>
       </c>
       <c r="M92" t="n">
-        <v>-0.4061721735699178</v>
+        <v>-0.3950721735699178</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>안정</t>
+          <t>모니터링</t>
         </is>
       </c>
       <c r="O92" t="inlineStr">
@@ -11441,7 +10891,7 @@
       </c>
       <c r="T92" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.260)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.406로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.272)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.395로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U92" t="inlineStr">
@@ -11473,12 +10923,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA92" t="n">
-        <v>35.5633248820733</v>
-      </c>
-      <c r="AB92" t="n">
-        <v>128.167910588026</v>
       </c>
     </row>
     <row r="93">
@@ -11512,7 +10956,7 @@
         <v>1</v>
       </c>
       <c r="H93" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I93" t="n">
         <v>0.1154682386344549</v>
@@ -11524,10 +10968,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L93" t="n">
-        <v>0.2384894128781516</v>
+        <v>0.2607227462114849</v>
       </c>
       <c r="M93" t="n">
-        <v>-0.428177253788515</v>
+        <v>-0.4059439204551817</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
@@ -11561,7 +11005,7 @@
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.238)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.428로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.261)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.406로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
@@ -11593,12 +11037,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA93" t="n">
-        <v>34.9840664224306</v>
-      </c>
-      <c r="AB93" t="n">
-        <v>128.320164576559</v>
       </c>
     </row>
     <row r="94">
@@ -11632,7 +11070,7 @@
         <v>1</v>
       </c>
       <c r="H94" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I94" t="n">
         <v>0.2559463474428509</v>
@@ -11644,10 +11082,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L94" t="n">
-        <v>0.1999139892936024</v>
+        <v>0.2110139892936024</v>
       </c>
       <c r="M94" t="n">
-        <v>-0.4667526773730643</v>
+        <v>-0.4556526773730643</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
@@ -11681,7 +11119,7 @@
       </c>
       <c r="T94" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.200)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.467로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.211)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.456로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U94" t="inlineStr">
@@ -11713,12 +11151,6 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA94" t="n">
-        <v>35.0627934125416</v>
-      </c>
-      <c r="AB94" t="n">
-        <v>127.747228685833</v>
       </c>
     </row>
     <row r="95">
@@ -11752,7 +11184,7 @@
         <v>1</v>
       </c>
       <c r="H95" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I95" t="n">
         <v>0.2361623444441073</v>
@@ -11764,10 +11196,10 @@
         <v>0.6666666666666666</v>
       </c>
       <c r="L95" t="n">
-        <v>0.1933193216273545</v>
+        <v>0.2044193216273545</v>
       </c>
       <c r="M95" t="n">
-        <v>-0.4733473450393121</v>
+        <v>-0.4622473450393121</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
@@ -11801,7 +11233,7 @@
       </c>
       <c r="T95" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.193)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.473로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.667)가 상담수요지수(CDI=0.204)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.462로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 상담인력 공급 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U95" t="inlineStr">
@@ -11833,23 +11265,17 @@
         <is>
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA95" t="n">
-        <v>35.5441279433078</v>
-      </c>
-      <c r="AB95" t="n">
-        <v>128.482361904572</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>480041958</t>
+          <t>480041300</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>김해수남고등학교</t>
+          <t>삼가고등학교</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -11859,35 +11285,35 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>합천군</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
       <c r="F96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="H96" t="n">
-        <v>1</v>
+        <v>0.3333</v>
       </c>
       <c r="I96" t="n">
-        <v>0.296344990720316</v>
+        <v>0.1721507225361336</v>
       </c>
       <c r="J96" t="n">
-        <v>0.07370330671481247</v>
+        <v>0.1818181818181819</v>
       </c>
       <c r="K96" t="n">
-        <v>0.6</v>
+        <v>0.3666666666666667</v>
       </c>
       <c r="L96" t="n">
-        <v>0.4566827658117095</v>
+        <v>0.2290896347847718</v>
       </c>
       <c r="M96" t="n">
-        <v>-0.1433172341882905</v>
+        <v>-0.1375770318818949</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
@@ -11896,47 +11322,47 @@
       </c>
       <c r="O96" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 보통</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>수요 보통</t>
+          <t>수요 낮음</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
         <is>
-          <t>A. 수요높음-공급낮음</t>
+          <t>C. 수요낮음-공급낮음</t>
         </is>
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>수요-공급 불균형 우선 개선</t>
+          <t>권역별 순회상담 또는 최소 인프라 보완</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T96" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.457)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.143로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.367)가 상담수요지수(CDI=0.229)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.138로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U96" t="inlineStr">
         <is>
-          <t>수요 중위</t>
+          <t>수요 하위</t>
         </is>
       </c>
       <c r="V96" t="inlineStr">
         <is>
-          <t>공급 중위</t>
+          <t>공급 하위</t>
         </is>
       </c>
       <c r="W96" t="inlineStr">
         <is>
-          <t>평균 관리형</t>
+          <t>최소 인프라 보완형</t>
         </is>
       </c>
       <c r="X96" t="inlineStr">
@@ -11946,30 +11372,24 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>weak:Wee센터접근성낮음</t>
+          <t>weak:Wee센터접근성낮음; matrix:인프라취약</t>
         </is>
       </c>
       <c r="Z96" t="inlineStr">
         <is>
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA96" t="n">
-        <v>35.168250344381</v>
-      </c>
-      <c r="AB96" t="n">
-        <v>128.816494912113</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>480041300</t>
+          <t>480041958</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>삼가고등학교</t>
+          <t>김해수남고등학교</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -11979,35 +11399,35 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>합천군</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G97" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="H97" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1721507225361336</v>
+        <v>0.296344990720316</v>
       </c>
       <c r="J97" t="n">
-        <v>0.1818181818181819</v>
+        <v>0.07370330671481247</v>
       </c>
       <c r="K97" t="n">
-        <v>0.3666666666666667</v>
+        <v>0.6</v>
       </c>
       <c r="L97" t="n">
-        <v>0.2179896347847718</v>
+        <v>0.4566827658117095</v>
       </c>
       <c r="M97" t="n">
-        <v>-0.1486770318818949</v>
+        <v>-0.1433172341882905</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
@@ -12016,47 +11436,47 @@
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>공급 보통</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q97" t="inlineStr">
         <is>
-          <t>C. 수요낮음-공급낮음</t>
+          <t>A. 수요높음-공급낮음</t>
         </is>
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>권역별 순회상담 또는 최소 인프라 보완</t>
+          <t>수요-공급 불균형 우선 개선</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>Wee클래스 신설 또는 운영 현황 재확인 검토; Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>Wee센터 접근성이 낮아 이동형 상담, 온라인 상담, 권역별 연계 강화 검토; 대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T97" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.367)가 상담수요지수(CDI=0.218)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.149로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.600)가 상담수요지수(CDI=0.457)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.143로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U97" t="inlineStr">
         <is>
-          <t>수요 하위</t>
+          <t>수요 중위</t>
         </is>
       </c>
       <c r="V97" t="inlineStr">
         <is>
-          <t>공급 하위</t>
+          <t>공급 중위</t>
         </is>
       </c>
       <c r="W97" t="inlineStr">
         <is>
-          <t>최소 인프라 보완형</t>
+          <t>평균 관리형</t>
         </is>
       </c>
       <c r="X97" t="inlineStr">
@@ -12066,19 +11486,13 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>weak:Wee센터접근성낮음; matrix:인프라취약</t>
+          <t>weak:Wee센터접근성낮음</t>
         </is>
       </c>
       <c r="Z97" t="inlineStr">
         <is>
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA97" t="n">
-        <v>35.4131367653631</v>
-      </c>
-      <c r="AB97" t="n">
-        <v>128.131377427692</v>
       </c>
     </row>
     <row r="98">
@@ -12112,7 +11526,7 @@
         <v>0.1</v>
       </c>
       <c r="H98" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I98" t="n">
         <v>0.2533219031874272</v>
@@ -12124,10 +11538,10 @@
         <v>0.3666666666666667</v>
       </c>
       <c r="L98" t="n">
-        <v>0.1844406343958091</v>
+        <v>0.195540634395809</v>
       </c>
       <c r="M98" t="n">
-        <v>-0.1822260322708576</v>
+        <v>-0.1711260322708577</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
@@ -12161,7 +11575,7 @@
       </c>
       <c r="T98" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.367)가 상담수요지수(CDI=0.184)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.182로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.367)가 상담수요지수(CDI=0.196)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.171로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U98" t="inlineStr">
@@ -12193,12 +11607,6 @@
         <is>
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA98" t="n">
-        <v>35.7032431448459</v>
-      </c>
-      <c r="AB98" t="n">
-        <v>128.169723246835</v>
       </c>
     </row>
     <row r="99">
@@ -12314,12 +11722,6 @@
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
       </c>
-      <c r="AA99" t="n">
-        <v>35.1124482199264</v>
-      </c>
-      <c r="AB99" t="n">
-        <v>128.749702620096</v>
-      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -12352,7 +11754,7 @@
         <v>0.4</v>
       </c>
       <c r="H100" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I100" t="n">
         <v>0.265045797380282</v>
@@ -12364,10 +11766,10 @@
         <v>0.4666666666666666</v>
       </c>
       <c r="L100" t="n">
-        <v>0.1883485991267607</v>
+        <v>0.1994485991267606</v>
       </c>
       <c r="M100" t="n">
-        <v>-0.278318067539906</v>
+        <v>-0.267218067539906</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
@@ -12401,7 +11803,7 @@
       </c>
       <c r="T100" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.188)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.278로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.467)가 상담수요지수(CDI=0.199)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.267로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee클래스 미운영, Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U100" t="inlineStr">
@@ -12433,12 +11835,6 @@
         <is>
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA100" t="n">
-        <v>35.0375271367234</v>
-      </c>
-      <c r="AB100" t="n">
-        <v>127.897878406914</v>
       </c>
     </row>
     <row r="101">
@@ -12472,7 +11868,7 @@
         <v>0.4</v>
       </c>
       <c r="H101" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I101" t="n">
         <v>0.0329226182635174</v>
@@ -12484,10 +11880,10 @@
         <v>0.7000000000000001</v>
       </c>
       <c r="L101" t="n">
-        <v>0.2574061478686181</v>
+        <v>0.2796394812019514</v>
       </c>
       <c r="M101" t="n">
-        <v>-0.442593852131382</v>
+        <v>-0.4203605187980486</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
@@ -12521,7 +11917,7 @@
       </c>
       <c r="T101" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.257)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.443로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.280)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.420로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U101" t="inlineStr">
@@ -12553,12 +11949,6 @@
         <is>
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA101" t="n">
-        <v>35.3864698488024</v>
-      </c>
-      <c r="AB101" t="n">
-        <v>128.472249036351</v>
       </c>
     </row>
     <row r="102">
@@ -12592,7 +11982,7 @@
         <v>0.4</v>
       </c>
       <c r="H102" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I102" t="n">
         <v>0.5170066198206746</v>
@@ -12604,10 +11994,10 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="L102" t="n">
-        <v>0.3166982850382641</v>
+        <v>0.3277982850382641</v>
       </c>
       <c r="M102" t="n">
-        <v>-0.4833017149617359</v>
+        <v>-0.4722017149617359</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
@@ -12641,7 +12031,7 @@
       </c>
       <c r="T102" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.317)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.483로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.328)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.472로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수, 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U102" t="inlineStr">
@@ -12673,12 +12063,6 @@
         <is>
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA102" t="n">
-        <v>34.9867799408032</v>
-      </c>
-      <c r="AB102" t="n">
-        <v>127.8401057682</v>
       </c>
     </row>
     <row r="103">
@@ -12712,7 +12096,7 @@
         <v>0.4</v>
       </c>
       <c r="H103" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I103" t="n">
         <v>0.454263085399187</v>
@@ -12724,10 +12108,10 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="L103" t="n">
-        <v>0.2514210284663956</v>
+        <v>0.2625210284663957</v>
       </c>
       <c r="M103" t="n">
-        <v>-0.5485789715336044</v>
+        <v>-0.5374789715336042</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
@@ -12761,7 +12145,7 @@
       </c>
       <c r="T103" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.251)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.549로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.263)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.537로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 Wee센터 접근성 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U103" t="inlineStr">
@@ -12793,23 +12177,17 @@
         <is>
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
-      </c>
-      <c r="AA103" t="n">
-        <v>35.6310841440155</v>
-      </c>
-      <c r="AB103" t="n">
-        <v>127.819862703751</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>480041188</t>
+          <t>480041840</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>김해삼문고등학교</t>
+          <t>진해세화여자고등학교</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -12819,7 +12197,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E104" t="n">
@@ -12835,19 +12213,19 @@
         <v>1</v>
       </c>
       <c r="I104" t="n">
-        <v>0.312149445577594</v>
+        <v>0.2667806965841105</v>
       </c>
       <c r="J104" t="n">
-        <v>0.06277819217900278</v>
+        <v>0.109802957036652</v>
       </c>
       <c r="K104" t="n">
         <v>0.6999999999999998</v>
       </c>
       <c r="L104" t="n">
-        <v>0.4583092125855322</v>
+        <v>0.4588612178735875</v>
       </c>
       <c r="M104" t="n">
-        <v>-0.2416907874144676</v>
+        <v>-0.2411387821264123</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
@@ -12881,7 +12259,7 @@
       </c>
       <c r="T104" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.458)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.242로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.459)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.241로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U104" t="inlineStr">
@@ -12913,23 +12291,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA104" t="n">
-        <v>35.1986298205938</v>
-      </c>
-      <c r="AB104" t="n">
-        <v>128.796661767766</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>480041924</t>
+          <t>480041188</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>해성고등학교</t>
+          <t>김해삼문고등학교</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -12939,7 +12311,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>거제시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E105" t="n">
@@ -12955,19 +12327,19 @@
         <v>1</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3178887908078384</v>
+        <v>0.312149445577594</v>
       </c>
       <c r="J105" t="n">
-        <v>0.05602835571511448</v>
+        <v>0.06277819217900278</v>
       </c>
       <c r="K105" t="n">
         <v>0.6999999999999998</v>
       </c>
       <c r="L105" t="n">
-        <v>0.4579723821743176</v>
+        <v>0.4583092125855322</v>
       </c>
       <c r="M105" t="n">
-        <v>-0.2420276178256822</v>
+        <v>-0.2416907874144676</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
@@ -13033,23 +12405,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA105" t="n">
-        <v>34.8706581895504</v>
-      </c>
-      <c r="AB105" t="n">
-        <v>128.723843213503</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>480041935</t>
+          <t>480041924</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>거제옥포고등학교</t>
+          <t>해성고등학교</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -13075,19 +12441,19 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>0.2855934776285337</v>
+        <v>0.3178887908078384</v>
       </c>
       <c r="J106" t="n">
-        <v>0.08495174255252685</v>
+        <v>0.05602835571511448</v>
       </c>
       <c r="K106" t="n">
         <v>0.6999999999999998</v>
       </c>
       <c r="L106" t="n">
-        <v>0.4568484067270202</v>
+        <v>0.4579723821743176</v>
       </c>
       <c r="M106" t="n">
-        <v>-0.2431515932729796</v>
+        <v>-0.2420276178256822</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
@@ -13121,7 +12487,7 @@
       </c>
       <c r="T106" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.457)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.243로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.458)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.242로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U106" t="inlineStr">
@@ -13153,23 +12519,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA106" t="n">
-        <v>34.9054080732463</v>
-      </c>
-      <c r="AB106" t="n">
-        <v>128.685992495653</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>480041258</t>
+          <t>480041935</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>마산내서여자고등학교</t>
+          <t>거제옥포고등학교</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -13179,7 +12539,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>거제시</t>
         </is>
       </c>
       <c r="E107" t="n">
@@ -13195,19 +12555,19 @@
         <v>1</v>
       </c>
       <c r="I107" t="n">
-        <v>0.2404186421316576</v>
+        <v>0.2855934776285337</v>
       </c>
       <c r="J107" t="n">
-        <v>0.1057539693932039</v>
+        <v>0.08495174255252685</v>
       </c>
       <c r="K107" t="n">
         <v>0.6999999999999998</v>
       </c>
       <c r="L107" t="n">
-        <v>0.4487242038416205</v>
+        <v>0.4568484067270202</v>
       </c>
       <c r="M107" t="n">
-        <v>-0.2512757961583794</v>
+        <v>-0.2431515932729796</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
@@ -13241,7 +12601,7 @@
       </c>
       <c r="T107" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.449)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.251로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.457)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.243로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U107" t="inlineStr">
@@ -13273,23 +12633,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA107" t="n">
-        <v>35.2372906222591</v>
-      </c>
-      <c r="AB107" t="n">
-        <v>128.502866678048</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>480041470</t>
+          <t>480041258</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>진해여자고등학교</t>
+          <t>마산내서여자고등학교</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -13315,19 +12669,19 @@
         <v>1</v>
       </c>
       <c r="I108" t="n">
-        <v>0.2465195827740016</v>
+        <v>0.2404186421316576</v>
       </c>
       <c r="J108" t="n">
-        <v>0.07679603054080128</v>
+        <v>0.1057539693932039</v>
       </c>
       <c r="K108" t="n">
         <v>0.6999999999999998</v>
       </c>
       <c r="L108" t="n">
-        <v>0.4411052044382677</v>
+        <v>0.4487242038416205</v>
       </c>
       <c r="M108" t="n">
-        <v>-0.2588947955617322</v>
+        <v>-0.2512757961583794</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
@@ -13361,7 +12715,7 @@
       </c>
       <c r="T108" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.441)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.259로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.449)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.251로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U108" t="inlineStr">
@@ -13393,23 +12747,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA108" t="n">
-        <v>35.1563022977092</v>
-      </c>
-      <c r="AB108" t="n">
-        <v>128.657512286037</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>480041848</t>
+          <t>480041470</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>진해중앙고등학교</t>
+          <t>진해여자고등학교</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -13435,19 +12783,19 @@
         <v>1</v>
       </c>
       <c r="I109" t="n">
-        <v>0.1905781927899014</v>
+        <v>0.2465195827740016</v>
       </c>
       <c r="J109" t="n">
-        <v>0.0403078947608462</v>
+        <v>0.07679603054080128</v>
       </c>
       <c r="K109" t="n">
         <v>0.6999999999999998</v>
       </c>
       <c r="L109" t="n">
-        <v>0.4102953625169158</v>
+        <v>0.4411052044382677</v>
       </c>
       <c r="M109" t="n">
-        <v>-0.2897046374830841</v>
+        <v>-0.2588947955617322</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
@@ -13481,7 +12829,7 @@
       </c>
       <c r="T109" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.410)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.290로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.441)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.259로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U109" t="inlineStr">
@@ -13513,23 +12861,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA109" t="n">
-        <v>35.1616317053989</v>
-      </c>
-      <c r="AB109" t="n">
-        <v>128.689397121305</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>480041510</t>
+          <t>480041848</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>통영고등학교</t>
+          <t>진해중앙고등학교</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -13539,7 +12881,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E110" t="n">
@@ -13555,19 +12897,19 @@
         <v>1</v>
       </c>
       <c r="I110" t="n">
-        <v>0.1538793933695575</v>
+        <v>0.1905781927899014</v>
       </c>
       <c r="J110" t="n">
-        <v>0.05379758396546978</v>
+        <v>0.0403078947608462</v>
       </c>
       <c r="K110" t="n">
         <v>0.6999999999999998</v>
       </c>
       <c r="L110" t="n">
-        <v>0.4025589924450091</v>
+        <v>0.4102953625169158</v>
       </c>
       <c r="M110" t="n">
-        <v>-0.2974410075549908</v>
+        <v>-0.2897046374830841</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
@@ -13601,7 +12943,7 @@
       </c>
       <c r="T110" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.403)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.297로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.410)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.290로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U110" t="inlineStr">
@@ -13633,23 +12975,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA110" t="n">
-        <v>34.8295473421071</v>
-      </c>
-      <c r="AB110" t="n">
-        <v>128.416198016185</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>480041221</t>
+          <t>480041510</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>창원북면고등학교</t>
+          <t>통영고등학교</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -13659,7 +12995,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="E111" t="n">
@@ -13675,19 +13011,19 @@
         <v>1</v>
       </c>
       <c r="I111" t="n">
-        <v>0.1144698988881103</v>
+        <v>0.1538793933695575</v>
       </c>
       <c r="J111" t="n">
-        <v>0.08689989448694277</v>
+        <v>0.05379758396546978</v>
       </c>
       <c r="K111" t="n">
         <v>0.6999999999999998</v>
       </c>
       <c r="L111" t="n">
-        <v>0.4004565977916844</v>
+        <v>0.4025589924450091</v>
       </c>
       <c r="M111" t="n">
-        <v>-0.2995434022083154</v>
+        <v>-0.2974410075549908</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
@@ -13721,7 +13057,7 @@
       </c>
       <c r="T111" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.400)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.300로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.403)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.297로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U111" t="inlineStr">
@@ -13753,23 +13089,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA111" t="n">
-        <v>35.2993649147603</v>
-      </c>
-      <c r="AB111" t="n">
-        <v>128.597256204529</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>480041346</t>
+          <t>480041221</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>김해삼방고등학교</t>
+          <t>창원북면고등학교</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -13779,7 +13109,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E112" t="n">
@@ -13789,25 +13119,25 @@
         <v>1</v>
       </c>
       <c r="G112" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H112" t="n">
         <v>1</v>
       </c>
       <c r="I112" t="n">
-        <v>0.2695858144944696</v>
+        <v>0.1144698988881103</v>
       </c>
       <c r="J112" t="n">
-        <v>0.1065812345637828</v>
+        <v>0.08689989448694277</v>
       </c>
       <c r="K112" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.6999999999999998</v>
       </c>
       <c r="L112" t="n">
-        <v>0.4587223496860842</v>
+        <v>0.4004565977916844</v>
       </c>
       <c r="M112" t="n">
-        <v>-0.3412776503139157</v>
+        <v>-0.2995434022083154</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
@@ -13841,7 +13171,7 @@
       </c>
       <c r="T112" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.459)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.341로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.700)가 상담수요지수(CDI=0.400)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.300로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U112" t="inlineStr">
@@ -13873,23 +13203,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA112" t="n">
-        <v>35.2553417806618</v>
-      </c>
-      <c r="AB112" t="n">
-        <v>128.903025424847</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>480041672</t>
+          <t>480041346</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>대아고등학교</t>
+          <t>김해삼방고등학교</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -13899,7 +13223,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E113" t="n">
@@ -13915,19 +13239,19 @@
         <v>1</v>
       </c>
       <c r="I113" t="n">
-        <v>0.2505327659675062</v>
+        <v>0.2695858144944696</v>
       </c>
       <c r="J113" t="n">
-        <v>0.05434060873858773</v>
+        <v>0.1065812345637828</v>
       </c>
       <c r="K113" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L113" t="n">
-        <v>0.434957791568698</v>
+        <v>0.4587223496860842</v>
       </c>
       <c r="M113" t="n">
-        <v>-0.3650422084313019</v>
+        <v>-0.3412776503139157</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
@@ -13961,7 +13285,7 @@
       </c>
       <c r="T113" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.435)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.365로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.459)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.341로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U113" t="inlineStr">
@@ -13993,23 +13317,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA113" t="n">
-        <v>35.1899281873726</v>
-      </c>
-      <c r="AB113" t="n">
-        <v>128.058388901858</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>480041445</t>
+          <t>480041654</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>증산고등학교</t>
+          <t>남해고등학교</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -14019,35 +13337,35 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>남해군</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
       </c>
       <c r="G114" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H114" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I114" t="n">
-        <v>0.2505681075971989</v>
+        <v>0.5272427649597402</v>
       </c>
       <c r="J114" t="n">
-        <v>0.05267763566246426</v>
+        <v>0.1303571428571429</v>
       </c>
       <c r="K114" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L114" t="n">
-        <v>0.434415247753221</v>
+        <v>0.4414333026056277</v>
       </c>
       <c r="M114" t="n">
-        <v>-0.3655847522467789</v>
+        <v>-0.3585666973943722</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
@@ -14076,12 +13394,12 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
         </is>
       </c>
       <c r="T114" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.434)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.366로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.441)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.359로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U114" t="inlineStr">
@@ -14113,23 +13431,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA114" t="n">
-        <v>35.3116625047773</v>
-      </c>
-      <c r="AB114" t="n">
-        <v>128.999412374335</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>480041786</t>
+          <t>480041672</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>양산제일고등학교</t>
+          <t>대아고등학교</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -14139,7 +13451,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E115" t="n">
@@ -14155,19 +13467,19 @@
         <v>1</v>
       </c>
       <c r="I115" t="n">
-        <v>0.2208455207621119</v>
+        <v>0.2505327659675062</v>
       </c>
       <c r="J115" t="n">
-        <v>0.08057910780812105</v>
+        <v>0.05434060873858773</v>
       </c>
       <c r="K115" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L115" t="n">
-        <v>0.433808209523411</v>
+        <v>0.434957791568698</v>
       </c>
       <c r="M115" t="n">
-        <v>-0.366191790476589</v>
+        <v>-0.3650422084313019</v>
       </c>
       <c r="N115" t="inlineStr">
         <is>
@@ -14201,7 +13513,7 @@
       </c>
       <c r="T115" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.434)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.366로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.435)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.365로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U115" t="inlineStr">
@@ -14233,23 +13545,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA115" t="n">
-        <v>35.3445999186343</v>
-      </c>
-      <c r="AB115" t="n">
-        <v>129.023799031436</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>480041355</t>
+          <t>480041445</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>양산남부고등학교</t>
+          <t>증산고등학교</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -14275,19 +13581,19 @@
         <v>1</v>
       </c>
       <c r="I116" t="n">
-        <v>0.191743779384035</v>
+        <v>0.2505681075971989</v>
       </c>
       <c r="J116" t="n">
-        <v>0.102956626419177</v>
+        <v>0.05267763566246426</v>
       </c>
       <c r="K116" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L116" t="n">
-        <v>0.4315668019344041</v>
+        <v>0.434415247753221</v>
       </c>
       <c r="M116" t="n">
-        <v>-0.3684331980655958</v>
+        <v>-0.3655847522467789</v>
       </c>
       <c r="N116" t="inlineStr">
         <is>
@@ -14321,7 +13627,7 @@
       </c>
       <c r="T116" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.432)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.368로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.434)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.366로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U116" t="inlineStr">
@@ -14353,23 +13659,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA116" t="n">
-        <v>35.3325819198917</v>
-      </c>
-      <c r="AB116" t="n">
-        <v>129.024749057257</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>480041931</t>
+          <t>480041786</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>창원대암고등학교</t>
+          <t>양산제일고등학교</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -14379,7 +13679,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E117" t="n">
@@ -14395,19 +13695,19 @@
         <v>1</v>
       </c>
       <c r="I117" t="n">
-        <v>0.2152890107824633</v>
+        <v>0.2208455207621119</v>
       </c>
       <c r="J117" t="n">
-        <v>0.05105071094104519</v>
+        <v>0.08057910780812105</v>
       </c>
       <c r="K117" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L117" t="n">
-        <v>0.4221132405745028</v>
+        <v>0.433808209523411</v>
       </c>
       <c r="M117" t="n">
-        <v>-0.3778867594254972</v>
+        <v>-0.366191790476589</v>
       </c>
       <c r="N117" t="inlineStr">
         <is>
@@ -14441,7 +13741,7 @@
       </c>
       <c r="T117" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.422)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.378로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.434)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.366로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U117" t="inlineStr">
@@ -14473,23 +13773,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA117" t="n">
-        <v>35.2074806828858</v>
-      </c>
-      <c r="AB117" t="n">
-        <v>128.711602507773</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>480041654</t>
+          <t>480041355</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>남해고등학교</t>
+          <t>양산남부고등학교</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -14499,35 +13793,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>남해군</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F118" t="n">
         <v>1</v>
       </c>
       <c r="G118" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H118" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5272427649597402</v>
+        <v>0.191743779384035</v>
       </c>
       <c r="J118" t="n">
-        <v>0.1303571428571429</v>
+        <v>0.102956626419177</v>
       </c>
       <c r="K118" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L118" t="n">
-        <v>0.4191999692722944</v>
+        <v>0.4315668019344041</v>
       </c>
       <c r="M118" t="n">
-        <v>-0.3808000307277055</v>
+        <v>-0.3684331980655958</v>
       </c>
       <c r="N118" t="inlineStr">
         <is>
@@ -14556,12 +13850,12 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T118" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.419)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.381로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.432)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.368로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U118" t="inlineStr">
@@ -14593,23 +13887,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA118" t="n">
-        <v>34.8028004626672</v>
-      </c>
-      <c r="AB118" t="n">
-        <v>127.951543024378</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>480041905</t>
+          <t>480041931</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>동원고등학교</t>
+          <t>창원대암고등학교</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -14619,7 +13907,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E119" t="n">
@@ -14635,19 +13923,19 @@
         <v>1</v>
       </c>
       <c r="I119" t="n">
-        <v>0.184001935767832</v>
+        <v>0.2152890107824633</v>
       </c>
       <c r="J119" t="n">
-        <v>0.07175893199765718</v>
+        <v>0.05105071094104519</v>
       </c>
       <c r="K119" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L119" t="n">
-        <v>0.4185869559218298</v>
+        <v>0.4221132405745028</v>
       </c>
       <c r="M119" t="n">
-        <v>-0.3814130440781701</v>
+        <v>-0.3778867594254972</v>
       </c>
       <c r="N119" t="inlineStr">
         <is>
@@ -14681,7 +13969,7 @@
       </c>
       <c r="T119" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.419)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.381로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.422)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.378로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U119" t="inlineStr">
@@ -14713,23 +14001,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA119" t="n">
-        <v>34.869521797481</v>
-      </c>
-      <c r="AB119" t="n">
-        <v>128.413205922052</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>480041474</t>
+          <t>480041905</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>창원봉림고등학교</t>
+          <t>동원고등학교</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -14739,7 +14021,7 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="E120" t="n">
@@ -14755,19 +14037,19 @@
         <v>1</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1574696928224008</v>
+        <v>0.184001935767832</v>
       </c>
       <c r="J120" t="n">
-        <v>0.08279367971131277</v>
+        <v>0.07175893199765718</v>
       </c>
       <c r="K120" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L120" t="n">
-        <v>0.4134211241779045</v>
+        <v>0.4185869559218298</v>
       </c>
       <c r="M120" t="n">
-        <v>-0.3865788758220954</v>
+        <v>-0.3814130440781701</v>
       </c>
       <c r="N120" t="inlineStr">
         <is>
@@ -14801,7 +14083,7 @@
       </c>
       <c r="T120" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.413)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.387로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.419)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.381로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U120" t="inlineStr">
@@ -14833,23 +14115,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA120" t="n">
-        <v>35.2483589527865</v>
-      </c>
-      <c r="AB120" t="n">
-        <v>128.676464476886</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>480041939</t>
+          <t>480041474</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>범어고등학교</t>
+          <t>창원봉림고등학교</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -14859,7 +14135,7 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E121" t="n">
@@ -14875,19 +14151,19 @@
         <v>1</v>
       </c>
       <c r="I121" t="n">
-        <v>0.1853057088977007</v>
+        <v>0.1574696928224008</v>
       </c>
       <c r="J121" t="n">
-        <v>0.04010538090266889</v>
+        <v>0.08279367971131277</v>
       </c>
       <c r="K121" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L121" t="n">
-        <v>0.4084703632667898</v>
+        <v>0.4134211241779045</v>
       </c>
       <c r="M121" t="n">
-        <v>-0.3915296367332101</v>
+        <v>-0.3865788758220954</v>
       </c>
       <c r="N121" t="inlineStr">
         <is>
@@ -14921,7 +14197,7 @@
       </c>
       <c r="T121" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.408)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.392로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.413)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.387로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U121" t="inlineStr">
@@ -14953,23 +14229,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA121" t="n">
-        <v>35.3297183526478</v>
-      </c>
-      <c r="AB121" t="n">
-        <v>129.018472823442</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>480041194</t>
+          <t>480041939</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>구산고등학교</t>
+          <t>범어고등학교</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -14979,7 +14249,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="E122" t="n">
@@ -14995,19 +14265,19 @@
         <v>1</v>
       </c>
       <c r="I122" t="n">
-        <v>0.1966784069560166</v>
+        <v>0.1853057088977007</v>
       </c>
       <c r="J122" t="n">
-        <v>0.02503219294887412</v>
+        <v>0.04010538090266889</v>
       </c>
       <c r="K122" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L122" t="n">
-        <v>0.4072368666349636</v>
+        <v>0.4084703632667898</v>
       </c>
       <c r="M122" t="n">
-        <v>-0.3927631333650363</v>
+        <v>-0.3915296367332101</v>
       </c>
       <c r="N122" t="inlineStr">
         <is>
@@ -15041,7 +14311,7 @@
       </c>
       <c r="T122" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.407)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.393로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.408)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.392로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U122" t="inlineStr">
@@ -15073,23 +14343,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA122" t="n">
-        <v>35.2504435908382</v>
-      </c>
-      <c r="AB122" t="n">
-        <v>128.875669406317</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>480041738</t>
+          <t>480041194</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>삼현여자고등학교</t>
+          <t>구산고등학교</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -15099,7 +14363,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>진주시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="E123" t="n">
@@ -15115,19 +14379,19 @@
         <v>1</v>
       </c>
       <c r="I123" t="n">
-        <v>0.1617593889078537</v>
+        <v>0.1966784069560166</v>
       </c>
       <c r="J123" t="n">
-        <v>0.05266445430851617</v>
+        <v>0.02503219294887412</v>
       </c>
       <c r="K123" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L123" t="n">
-        <v>0.40480794773879</v>
+        <v>0.4072368666349636</v>
       </c>
       <c r="M123" t="n">
-        <v>-0.39519205226121</v>
+        <v>-0.3927631333650363</v>
       </c>
       <c r="N123" t="inlineStr">
         <is>
@@ -15161,7 +14425,7 @@
       </c>
       <c r="T123" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.405)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.395로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.407)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.393로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U123" t="inlineStr">
@@ -15193,23 +14457,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA123" t="n">
-        <v>35.1774044091928</v>
-      </c>
-      <c r="AB123" t="n">
-        <v>128.11204049237</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>480041636</t>
+          <t>480041738</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>경해여자고등학교</t>
+          <t>삼현여자고등학교</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -15235,19 +14493,19 @@
         <v>1</v>
       </c>
       <c r="I124" t="n">
-        <v>0.1883641448245586</v>
+        <v>0.1617593889078537</v>
       </c>
       <c r="J124" t="n">
-        <v>0.02197802197802198</v>
+        <v>0.05266445430851617</v>
       </c>
       <c r="K124" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L124" t="n">
-        <v>0.4034473889341935</v>
+        <v>0.40480794773879</v>
       </c>
       <c r="M124" t="n">
-        <v>-0.3965526110658064</v>
+        <v>-0.39519205226121</v>
       </c>
       <c r="N124" t="inlineStr">
         <is>
@@ -15281,7 +14539,7 @@
       </c>
       <c r="T124" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.403)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.397로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.405)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.395로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U124" t="inlineStr">
@@ -15313,23 +14571,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA124" t="n">
-        <v>35.165171069982</v>
-      </c>
-      <c r="AB124" t="n">
-        <v>128.041709691013</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>480041846</t>
+          <t>480041636</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>진주동명고등학교</t>
+          <t>경해여자고등학교</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -15355,19 +14607,19 @@
         <v>1</v>
       </c>
       <c r="I125" t="n">
-        <v>0.0765532478720137</v>
+        <v>0.1883641448245586</v>
       </c>
       <c r="J125" t="n">
-        <v>0.1084173804918486</v>
+        <v>0.02197802197802198</v>
       </c>
       <c r="K125" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L125" t="n">
-        <v>0.3949902094546208</v>
+        <v>0.4034473889341935</v>
       </c>
       <c r="M125" t="n">
-        <v>-0.4050097905453791</v>
+        <v>-0.3965526110658064</v>
       </c>
       <c r="N125" t="inlineStr">
         <is>
@@ -15401,7 +14653,7 @@
       </c>
       <c r="T125" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.395)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.405로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.403)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.397로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U125" t="inlineStr">
@@ -15433,23 +14685,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA125" t="n">
-        <v>35.2025448243018</v>
-      </c>
-      <c r="AB125" t="n">
-        <v>128.118939619607</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>480041882</t>
+          <t>480041846</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>창원고등학교</t>
+          <t>진주동명고등학교</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -15459,7 +14705,7 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>진주시</t>
         </is>
       </c>
       <c r="E126" t="n">
@@ -15475,19 +14721,19 @@
         <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>0.06255106816287991</v>
+        <v>0.0765532478720137</v>
       </c>
       <c r="J126" t="n">
-        <v>0.06535548537331762</v>
+        <v>0.1084173804918486</v>
       </c>
       <c r="K126" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L126" t="n">
-        <v>0.3759688511787325</v>
+        <v>0.3949902094546208</v>
       </c>
       <c r="M126" t="n">
-        <v>-0.4240311488212674</v>
+        <v>-0.4050097905453791</v>
       </c>
       <c r="N126" t="inlineStr">
         <is>
@@ -15521,7 +14767,7 @@
       </c>
       <c r="T126" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.376)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.424로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.395)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.405로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U126" t="inlineStr">
@@ -15553,23 +14799,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA126" t="n">
-        <v>35.2552857661663</v>
-      </c>
-      <c r="AB126" t="n">
-        <v>128.642705069512</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>480041001</t>
+          <t>480041882</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>경상고등학교</t>
+          <t>창원고등학교</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -15595,19 +14835,19 @@
         <v>1</v>
       </c>
       <c r="I127" t="n">
-        <v>0.0585764310226926</v>
+        <v>0.06255106816287991</v>
       </c>
       <c r="J127" t="n">
-        <v>0</v>
+        <v>0.06535548537331762</v>
       </c>
       <c r="K127" t="n">
         <v>0.7999999999999999</v>
       </c>
       <c r="L127" t="n">
-        <v>0.3528588103408976</v>
+        <v>0.3759688511787325</v>
       </c>
       <c r="M127" t="n">
-        <v>-0.4471411896591023</v>
+        <v>-0.4240311488212674</v>
       </c>
       <c r="N127" t="inlineStr">
         <is>
@@ -15641,7 +14881,7 @@
       </c>
       <c r="T127" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.353)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.447로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.376)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.424로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U127" t="inlineStr">
@@ -15673,23 +14913,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA127" t="n">
-        <v>35.2609674499282</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>128.600515443896</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>480041608</t>
+          <t>480041001</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>대성일고등학교</t>
+          <t>경상고등학교</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -15699,11 +14933,11 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>거창군</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="F128" t="n">
         <v>1</v>
@@ -15712,22 +14946,22 @@
         <v>1</v>
       </c>
       <c r="H128" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
-        <v>0.4817851398830783</v>
+        <v>0.0585764310226926</v>
       </c>
       <c r="J128" t="n">
-        <v>0.2339320004518243</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>0.9</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L128" t="n">
-        <v>0.4385723801116342</v>
+        <v>0.3528588103408976</v>
       </c>
       <c r="M128" t="n">
-        <v>-0.4614276198883658</v>
+        <v>-0.4471411896591023</v>
       </c>
       <c r="N128" t="inlineStr">
         <is>
@@ -15736,7 +14970,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>공급 높음</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P128" t="inlineStr">
@@ -15746,22 +14980,22 @@
       </c>
       <c r="Q128" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>실제 상담 이용 수준이 높아 상담 프로그램 확대 또는 상담 인력 보완 검토; 학교폭력 피해 응답률 기반 위험 점수가 높아 학교폭력 관련 상담지원 강화 검토</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T128" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.439)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.461로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.353)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.447로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U128" t="inlineStr">
@@ -15771,12 +15005,12 @@
       </c>
       <c r="V128" t="inlineStr">
         <is>
-          <t>공급 상위</t>
+          <t>공급 중위</t>
         </is>
       </c>
       <c r="W128" t="inlineStr">
         <is>
-          <t>안정 관리형</t>
+          <t>평균 관리형</t>
         </is>
       </c>
       <c r="X128" t="inlineStr">
@@ -15793,12 +15027,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA128" t="n">
-        <v>35.6910833838131</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>127.900360575893</v>
       </c>
     </row>
     <row r="129">
@@ -15832,7 +15060,7 @@
         <v>0.7</v>
       </c>
       <c r="H129" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I129" t="n">
         <v>0.2674391673483604</v>
@@ -15844,10 +15072,10 @@
         <v>0.7999999999999999</v>
       </c>
       <c r="L129" t="n">
-        <v>0.3195301616780152</v>
+        <v>0.3417634950113486</v>
       </c>
       <c r="M129" t="n">
-        <v>-0.4804698383219848</v>
+        <v>-0.4582365049886513</v>
       </c>
       <c r="N129" t="inlineStr">
         <is>
@@ -15881,7 +15109,7 @@
       </c>
       <c r="T129" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.320)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.480로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.342)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.458로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U129" t="inlineStr">
@@ -15913,12 +15141,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA129" t="n">
-        <v>35.167490215805</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>128.571168595676</v>
       </c>
     </row>
     <row r="130">
@@ -15952,7 +15174,7 @@
         <v>1</v>
       </c>
       <c r="H130" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I130" t="n">
         <v>0.4936783384019001</v>
@@ -15964,10 +15186,10 @@
         <v>0.9</v>
       </c>
       <c r="L130" t="n">
-        <v>0.3994221774928415</v>
+        <v>0.4216555108261748</v>
       </c>
       <c r="M130" t="n">
-        <v>-0.5005778225071585</v>
+        <v>-0.4783444891738252</v>
       </c>
       <c r="N130" t="inlineStr">
         <is>
@@ -16001,7 +15223,7 @@
       </c>
       <c r="T130" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.399)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.501로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.422)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.478로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U130" t="inlineStr">
@@ -16033,23 +15255,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA130" t="n">
-        <v>35.4937858569008</v>
-      </c>
-      <c r="AB130" t="n">
-        <v>128.746783406621</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>480041901</t>
+          <t>480041633</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>충렬여자고등학교</t>
+          <t>고성고등학교</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -16059,7 +15275,7 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>통영시</t>
+          <t>고성군</t>
         </is>
       </c>
       <c r="E131" t="n">
@@ -16069,25 +15285,25 @@
         <v>1</v>
       </c>
       <c r="G131" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="H131" t="n">
-        <v>1</v>
+        <v>0.6667</v>
       </c>
       <c r="I131" t="n">
-        <v>0.1345182690610425</v>
+        <v>0.2611738807004353</v>
       </c>
       <c r="J131" t="n">
-        <v>0.03025292194370326</v>
+        <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>0.9</v>
+        <v>0.7999999999999999</v>
       </c>
       <c r="L131" t="n">
-        <v>0.3882570636682486</v>
+        <v>0.3092912935668117</v>
       </c>
       <c r="M131" t="n">
-        <v>-0.5117429363317514</v>
+        <v>-0.4907087064331883</v>
       </c>
       <c r="N131" t="inlineStr">
         <is>
@@ -16096,7 +15312,7 @@
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>공급 높음</t>
+          <t>공급 양호</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
@@ -16106,22 +15322,22 @@
       </c>
       <c r="Q131" t="inlineStr">
         <is>
-          <t>B. 수요높음-공급높음</t>
+          <t>D. 수요낮음-공급높음</t>
         </is>
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>고수요 학교 모니터링 및 프로그램 강화</t>
+          <t>현 수준 유지 또는 거점학교 활용</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
+          <t>현 수준 유지 및 정기 모니터링</t>
         </is>
       </c>
       <c r="T131" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.388)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.512로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.309)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.491로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U131" t="inlineStr">
@@ -16131,12 +15347,12 @@
       </c>
       <c r="V131" t="inlineStr">
         <is>
-          <t>공급 상위</t>
+          <t>공급 중위</t>
         </is>
       </c>
       <c r="W131" t="inlineStr">
         <is>
-          <t>안정 관리형</t>
+          <t>평균 관리형</t>
         </is>
       </c>
       <c r="X131" t="inlineStr">
@@ -16153,23 +15369,17 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA131" t="n">
-        <v>34.8868877467241</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>128.465049182599</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>480041633</t>
+          <t>480041901</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>고성고등학교</t>
+          <t>충렬여자고등학교</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -16179,7 +15389,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>고성군</t>
+          <t>통영시</t>
         </is>
       </c>
       <c r="E132" t="n">
@@ -16189,25 +15399,25 @@
         <v>1</v>
       </c>
       <c r="G132" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
       <c r="H132" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="I132" t="n">
-        <v>0.2611738807004353</v>
+        <v>0.1345182690610425</v>
       </c>
       <c r="J132" t="n">
-        <v>0</v>
+        <v>0.03025292194370326</v>
       </c>
       <c r="K132" t="n">
-        <v>0.7999999999999999</v>
+        <v>0.9</v>
       </c>
       <c r="L132" t="n">
-        <v>0.2870579602334784</v>
+        <v>0.3882570636682486</v>
       </c>
       <c r="M132" t="n">
-        <v>-0.5129420397665215</v>
+        <v>-0.5117429363317514</v>
       </c>
       <c r="N132" t="inlineStr">
         <is>
@@ -16216,32 +15426,32 @@
       </c>
       <c r="O132" t="inlineStr">
         <is>
-          <t>공급 양호</t>
+          <t>공급 높음</t>
         </is>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>수요 낮음</t>
+          <t>수요 보통</t>
         </is>
       </c>
       <c r="Q132" t="inlineStr">
         <is>
-          <t>D. 수요낮음-공급높음</t>
+          <t>B. 수요높음-공급높음</t>
         </is>
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>현 수준 유지 또는 거점학교 활용</t>
+          <t>고수요 학교 모니터링 및 프로그램 강화</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>현 수준 유지 및 정기 모니터링</t>
+          <t>대규모 학교로 상담수요 규모가 커 상담 인력 보강 검토</t>
         </is>
       </c>
       <c r="T132" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.800)가 상담수요지수(CDI=0.287)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.513로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.388)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.512로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U132" t="inlineStr">
@@ -16251,12 +15461,12 @@
       </c>
       <c r="V132" t="inlineStr">
         <is>
-          <t>공급 중위</t>
+          <t>공급 상위</t>
         </is>
       </c>
       <c r="W132" t="inlineStr">
         <is>
-          <t>평균 관리형</t>
+          <t>안정 관리형</t>
         </is>
       </c>
       <c r="X132" t="inlineStr">
@@ -16273,12 +15483,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA132" t="n">
-        <v>35.0556838834298</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>128.362571773184</v>
       </c>
     </row>
     <row r="133">
@@ -16312,7 +15516,7 @@
         <v>1</v>
       </c>
       <c r="H133" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I133" t="n">
         <v>0.3981295677618628</v>
@@ -16324,10 +15528,10 @@
         <v>0.9</v>
       </c>
       <c r="L133" t="n">
-        <v>0.3561690715057095</v>
+        <v>0.3784024048390429</v>
       </c>
       <c r="M133" t="n">
-        <v>-0.5438309284942906</v>
+        <v>-0.5215975951609571</v>
       </c>
       <c r="N133" t="inlineStr">
         <is>
@@ -16361,7 +15565,7 @@
       </c>
       <c r="T133" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.356)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.544로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.378)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.522로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U133" t="inlineStr">
@@ -16393,12 +15597,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA133" t="n">
-        <v>35.6930826295593</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>127.902909247685</v>
       </c>
     </row>
     <row r="134">
@@ -16432,7 +15630,7 @@
         <v>1</v>
       </c>
       <c r="H134" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I134" t="n">
         <v>0.3808201961902997</v>
@@ -16444,10 +15642,10 @@
         <v>0.9</v>
       </c>
       <c r="L134" t="n">
-        <v>0.3465479085340215</v>
+        <v>0.3687812418673548</v>
       </c>
       <c r="M134" t="n">
-        <v>-0.5534520914659785</v>
+        <v>-0.5312187581326453</v>
       </c>
       <c r="N134" t="inlineStr">
         <is>
@@ -16481,7 +15679,7 @@
       </c>
       <c r="T134" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.347)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.553로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.369)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.531로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U134" t="inlineStr">
@@ -16513,12 +15711,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA134" t="n">
-        <v>35.2725144557426</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>128.402479825779</v>
       </c>
     </row>
     <row r="135">
@@ -16552,7 +15744,7 @@
         <v>1</v>
       </c>
       <c r="H135" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I135" t="n">
         <v>0.3240687900487338</v>
@@ -16564,10 +15756,10 @@
         <v>0.9</v>
       </c>
       <c r="L135" t="n">
-        <v>0.331761994710056</v>
+        <v>0.3539953280433893</v>
       </c>
       <c r="M135" t="n">
-        <v>-0.5682380052899441</v>
+        <v>-0.5460046719566107</v>
       </c>
       <c r="N135" t="inlineStr">
         <is>
@@ -16601,7 +15793,7 @@
       </c>
       <c r="T135" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.332)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.568로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.354)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.546로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U135" t="inlineStr">
@@ -16633,12 +15825,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA135" t="n">
-        <v>35.2278895605022</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>128.661226194879</v>
       </c>
     </row>
     <row r="136">
@@ -16672,7 +15858,7 @@
         <v>1</v>
       </c>
       <c r="H136" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I136" t="n">
         <v>0.2718666795525124</v>
@@ -16684,10 +15870,10 @@
         <v>0.9</v>
       </c>
       <c r="L136" t="n">
-        <v>0.3271729027311277</v>
+        <v>0.349406236064461</v>
       </c>
       <c r="M136" t="n">
-        <v>-0.5728270972688723</v>
+        <v>-0.550593763935539</v>
       </c>
       <c r="N136" t="inlineStr">
         <is>
@@ -16721,7 +15907,7 @@
       </c>
       <c r="T136" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.327)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.573로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.349)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.551로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
@@ -16753,12 +15939,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA136" t="n">
-        <v>35.2142531567645</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>128.692425901257</v>
       </c>
     </row>
     <row r="137">
@@ -16792,7 +15972,7 @@
         <v>1</v>
       </c>
       <c r="H137" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I137" t="n">
         <v>0.2865279309795805</v>
@@ -16804,10 +15984,10 @@
         <v>0.9</v>
       </c>
       <c r="L137" t="n">
-        <v>0.3258272363934743</v>
+        <v>0.3480605697268076</v>
       </c>
       <c r="M137" t="n">
-        <v>-0.5741727636065257</v>
+        <v>-0.5519394302731924</v>
       </c>
       <c r="N137" t="inlineStr">
         <is>
@@ -16841,7 +16021,7 @@
       </c>
       <c r="T137" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.326)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.574로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.348)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.552로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U137" t="inlineStr">
@@ -16873,12 +16053,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA137" t="n">
-        <v>34.9345453558444</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>128.077701048261</v>
       </c>
     </row>
     <row r="138">
@@ -16912,7 +16086,7 @@
         <v>1</v>
       </c>
       <c r="H138" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I138" t="n">
         <v>0.3595670410503039</v>
@@ -16924,10 +16098,10 @@
         <v>0.9</v>
       </c>
       <c r="L138" t="n">
-        <v>0.3198556803501013</v>
+        <v>0.3420890136834346</v>
       </c>
       <c r="M138" t="n">
-        <v>-0.5801443196498988</v>
+        <v>-0.5579109863165654</v>
       </c>
       <c r="N138" t="inlineStr">
         <is>
@@ -16961,7 +16135,7 @@
       </c>
       <c r="T138" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.320)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.580로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.342)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.558로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U138" t="inlineStr">
@@ -16993,12 +16167,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA138" t="n">
-        <v>35.197939246733</v>
-      </c>
-      <c r="AB138" t="n">
-        <v>128.559832051422</v>
       </c>
     </row>
     <row r="139">
@@ -17032,7 +16200,7 @@
         <v>1</v>
       </c>
       <c r="H139" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I139" t="n">
         <v>0.2004335900090441</v>
@@ -17044,10 +16212,10 @@
         <v>0.9</v>
       </c>
       <c r="L139" t="n">
-        <v>0.2753218349675537</v>
+        <v>0.297555168300887</v>
       </c>
       <c r="M139" t="n">
-        <v>-0.6246781650324463</v>
+        <v>-0.602444831699113</v>
       </c>
       <c r="N139" t="inlineStr">
         <is>
@@ -17081,7 +16249,7 @@
       </c>
       <c r="T139" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.275)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.625로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.298)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.602로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U139" t="inlineStr">
@@ -17113,12 +16281,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA139" t="n">
-        <v>35.6903560029964</v>
-      </c>
-      <c r="AB139" t="n">
-        <v>127.904026348041</v>
       </c>
     </row>
     <row r="140">
@@ -17152,7 +16314,7 @@
         <v>1</v>
       </c>
       <c r="H140" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I140" t="n">
         <v>0.1478611366284428</v>
@@ -17164,10 +16326,10 @@
         <v>0.9</v>
       </c>
       <c r="L140" t="n">
-        <v>0.2729090927869087</v>
+        <v>0.2951424261202421</v>
       </c>
       <c r="M140" t="n">
-        <v>-0.6270909072130912</v>
+        <v>-0.6048575738797579</v>
       </c>
       <c r="N140" t="inlineStr">
         <is>
@@ -17201,7 +16363,7 @@
       </c>
       <c r="T140" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.273)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.627로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.295)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.605로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U140" t="inlineStr">
@@ -17233,12 +16395,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA140" t="n">
-        <v>35.6930116467922</v>
-      </c>
-      <c r="AB140" t="n">
-        <v>127.909786939337</v>
       </c>
     </row>
     <row r="141">
@@ -17272,7 +16428,7 @@
         <v>0.7</v>
       </c>
       <c r="H141" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I141" t="n">
         <v>0.4071925075669307</v>
@@ -17284,10 +16440,10 @@
         <v>0.9</v>
       </c>
       <c r="L141" t="n">
-        <v>0.2563493925566745</v>
+        <v>0.2674493925566745</v>
       </c>
       <c r="M141" t="n">
-        <v>-0.6436506074433255</v>
+        <v>-0.6325506074433256</v>
       </c>
       <c r="N141" t="inlineStr">
         <is>
@@ -17321,7 +16477,7 @@
       </c>
       <c r="T141" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.256)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.644로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.267)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.633로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U141" t="inlineStr">
@@ -17353,12 +16509,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA141" t="n">
-        <v>35.601349513552</v>
-      </c>
-      <c r="AB141" t="n">
-        <v>128.461516288182</v>
       </c>
     </row>
     <row r="142">
@@ -17392,7 +16542,7 @@
         <v>1</v>
       </c>
       <c r="H142" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I142" t="n">
         <v>0.0255824556496562</v>
@@ -17404,10 +16554,10 @@
         <v>0.9</v>
       </c>
       <c r="L142" t="n">
-        <v>0.2388079746087166</v>
+        <v>0.2610413079420499</v>
       </c>
       <c r="M142" t="n">
-        <v>-0.6611920253912834</v>
+        <v>-0.6389586920579502</v>
       </c>
       <c r="N142" t="inlineStr">
         <is>
@@ -17441,7 +16591,7 @@
       </c>
       <c r="T142" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.239)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.661로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.261)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.639로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U142" t="inlineStr">
@@ -17473,12 +16623,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA142" t="n">
-        <v>34.9427082511284</v>
-      </c>
-      <c r="AB142" t="n">
-        <v>128.08481669409</v>
       </c>
     </row>
     <row r="143">
@@ -17512,7 +16656,7 @@
         <v>1</v>
       </c>
       <c r="H143" t="n">
-        <v>0.6</v>
+        <v>0.6667</v>
       </c>
       <c r="I143" t="n">
         <v>0.1131027623352295</v>
@@ -17524,10 +16668,10 @@
         <v>0.9</v>
       </c>
       <c r="L143" t="n">
-        <v>0.2377009207784098</v>
+        <v>0.2599342541117431</v>
       </c>
       <c r="M143" t="n">
-        <v>-0.6622990792215903</v>
+        <v>-0.6400657458882569</v>
       </c>
       <c r="N143" t="inlineStr">
         <is>
@@ -17561,7 +16705,7 @@
       </c>
       <c r="T143" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.238)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.662로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=0.900)가 상담수요지수(CDI=0.260)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.640로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U143" t="inlineStr">
@@ -17593,12 +16737,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA143" t="n">
-        <v>35.4100168211844</v>
-      </c>
-      <c r="AB143" t="n">
-        <v>127.871096164153</v>
       </c>
     </row>
     <row r="144">
@@ -17632,7 +16770,7 @@
         <v>1</v>
       </c>
       <c r="H144" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I144" t="n">
         <v>0.3982246984762633</v>
@@ -17644,10 +16782,10 @@
         <v>1</v>
       </c>
       <c r="L144" t="n">
-        <v>0.2527415661587544</v>
+        <v>0.2638415661587545</v>
       </c>
       <c r="M144" t="n">
-        <v>-0.7472584338412456</v>
+        <v>-0.7361584338412455</v>
       </c>
       <c r="N144" t="inlineStr">
         <is>
@@ -17681,7 +16819,7 @@
       </c>
       <c r="T144" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.253)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.747로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.264)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.736로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U144" t="inlineStr">
@@ -17713,12 +16851,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA144" t="n">
-        <v>35.5635332170554</v>
-      </c>
-      <c r="AB144" t="n">
-        <v>128.154572589335</v>
       </c>
     </row>
     <row r="145">
@@ -17752,7 +16884,7 @@
         <v>1</v>
       </c>
       <c r="H145" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I145" t="n">
         <v>0.3164180297242954</v>
@@ -17764,10 +16896,10 @@
         <v>1</v>
       </c>
       <c r="L145" t="n">
-        <v>0.2428185164219077</v>
+        <v>0.2539185164219077</v>
       </c>
       <c r="M145" t="n">
-        <v>-0.7571814835780923</v>
+        <v>-0.7460814835780922</v>
       </c>
       <c r="N145" t="inlineStr">
         <is>
@@ -17801,7 +16933,7 @@
       </c>
       <c r="T145" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.243)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.757로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.254)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.746로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U145" t="inlineStr">
@@ -17833,12 +16965,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA145" t="n">
-        <v>35.5403709329672</v>
-      </c>
-      <c r="AB145" t="n">
-        <v>128.505359650254</v>
       </c>
     </row>
     <row r="146">
@@ -17872,7 +16998,7 @@
         <v>1</v>
       </c>
       <c r="H146" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I146" t="n">
         <v>0.1976726557730393</v>
@@ -17884,10 +17010,10 @@
         <v>1</v>
       </c>
       <c r="L146" t="n">
-        <v>0.2045189238857184</v>
+        <v>0.2156189238857184</v>
       </c>
       <c r="M146" t="n">
-        <v>-0.7954810761142816</v>
+        <v>-0.7843810761142815</v>
       </c>
       <c r="N146" t="inlineStr">
         <is>
@@ -17921,7 +17047,7 @@
       </c>
       <c r="T146" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.205)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.795로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.216)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.784로, 공급이 수요보다 높거나 비슷한 상태이다. 특히 학교폭력 위험 점수이 취약하여 관련 지원 검토가 필요하다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U146" t="inlineStr">
@@ -17953,12 +17079,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA146" t="n">
-        <v>35.3227017364893</v>
-      </c>
-      <c r="AB146" t="n">
-        <v>128.265590219129</v>
       </c>
     </row>
     <row r="147">
@@ -17992,7 +17112,7 @@
         <v>1</v>
       </c>
       <c r="H147" t="n">
-        <v>0.3</v>
+        <v>0.3333</v>
       </c>
       <c r="I147" t="n">
         <v>0.2051374145411299</v>
@@ -18004,10 +17124,10 @@
         <v>1</v>
       </c>
       <c r="L147" t="n">
-        <v>0.1791899489911875</v>
+        <v>0.1902899489911875</v>
       </c>
       <c r="M147" t="n">
-        <v>-0.8208100510088125</v>
+        <v>-0.8097100510088124</v>
       </c>
       <c r="N147" t="inlineStr">
         <is>
@@ -18041,7 +17161,7 @@
       </c>
       <c r="T147" t="inlineStr">
         <is>
-          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.179)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.821로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
+          <t>해당 학교는 상담공급지수(CSI=1.000)가 상담수요지수(CDI=0.190)보다 높아 현재 공급이 수요를 상대적으로 충족하는 것으로 분류된다. 우선지원점수는 -0.810로, 공급이 수요보다 높거나 비슷한 상태이다. 주요 하위 점수에서 두드러진 취약 항목은 확인되지 않는다. 이 결과는 실제 지원 확정이 아니라 정책 검토 우선순위를 나타내며, 현장 의견 및 추가 검토를 거쳐 최종 판단해야 한다.</t>
         </is>
       </c>
       <c r="U147" t="inlineStr">
@@ -18073,12 +17193,6 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
-      </c>
-      <c r="AA147" t="n">
-        <v>35.6767927637267</v>
-      </c>
-      <c r="AB147" t="n">
-        <v>127.912929627495</v>
       </c>
     </row>
   </sheetData>
@@ -18092,7 +17206,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18164,276 +17278,316 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7092000000000001</v>
+        <v>0.7095</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4971</v>
+        <v>0.5001</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2121</v>
+        <v>-0.2094</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2724</v>
+        <v>0.2679</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0.8552</v>
+        <v>0.8607</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9724</v>
+        <v>0.9762</v>
       </c>
       <c r="J2" t="n">
-        <v>0.4214</v>
+        <v>0.4269</v>
       </c>
       <c r="K2" t="n">
-        <v>0.09760000000000001</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>19.9</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>잠재 취약형</t>
+          <t>고수요 유지관리형</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>0.319</v>
+        <v>0.9</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3862</v>
+        <v>0.4608</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0672</v>
+        <v>-0.4392</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="G3" t="n">
-        <v>0.6429</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3143</v>
+        <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7071</v>
+        <v>0.6667</v>
       </c>
       <c r="J3" t="n">
-        <v>0.2334</v>
+        <v>0.4818</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2181</v>
+        <v>0.2339</v>
       </c>
       <c r="L3" t="n">
-        <v>9.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>평균 관리형</t>
+          <t>잠재 취약형</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>63</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7026</v>
+        <v>0.319</v>
       </c>
       <c r="D4" t="n">
-        <v>0.3897</v>
+        <v>0.3966</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3129</v>
+        <v>0.0775</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2079</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>0.6429</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9</v>
+        <v>0.3143</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8524</v>
+        <v>0.7381</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2455</v>
+        <v>0.2334</v>
       </c>
       <c r="K4" t="n">
-        <v>0.07140000000000001</v>
+        <v>0.2181</v>
       </c>
       <c r="L4" t="n">
-        <v>43.2</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>안정 관리형</t>
+          <t>평균 관리형</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9</v>
+        <v>0.7026</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3438</v>
+        <v>0.3976</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5562</v>
+        <v>-0.305</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7</v>
+        <v>0.2109</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0.8969</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6364</v>
+        <v>0.875</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3163</v>
+        <v>0.2458</v>
       </c>
       <c r="K5" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>7.5</v>
+        <v>43.8</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>최소 인프라 보완형</t>
+          <t>안정 관리형</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3156</v>
+        <v>0.9</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2057</v>
+        <v>0.3543</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1099</v>
+        <v>-0.5457</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2</v>
+        <v>0.7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2667</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
-        <v>0.36</v>
+        <v>0.7</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2102</v>
+        <v>0.2997</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0468</v>
+        <v>0.06320000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>10.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>안정 모니터링형</t>
+          <t>최소 인프라 보완형</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6762</v>
+        <v>0.3156</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2314</v>
+        <v>0.219</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4448</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2429</v>
+        <v>0.2</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>0.2667</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7857</v>
+        <v>0.48</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3857</v>
+        <v>0.4</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2531</v>
+        <v>0.2102</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0554</v>
+        <v>0.0468</v>
       </c>
       <c r="L7" t="n">
-        <v>4.8</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>여유·거점 활용형</t>
+          <t>안정 모니터링형</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>7</v>
       </c>
       <c r="C8" t="n">
+        <v>0.6762</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.2457</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-0.4305</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.2429</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.7857</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.2531</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.0554</v>
+      </c>
+      <c r="L8" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>여유·거점 활용형</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="n">
         <v>0.9571</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.2303</v>
-      </c>
-      <c r="E8" t="n">
-        <v>-0.7268</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="D9" t="n">
+        <v>0.2446</v>
+      </c>
+      <c r="E9" t="n">
+        <v>-0.7126</v>
+      </c>
+      <c r="F9" t="n">
         <v>0.9143</v>
       </c>
-      <c r="G8" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>0.9571</v>
       </c>
-      <c r="I8" t="n">
-        <v>0.3857</v>
-      </c>
-      <c r="J8" t="n">
+      <c r="I9" t="n">
+        <v>0.4286</v>
+      </c>
+      <c r="J9" t="n">
         <v>0.2376</v>
       </c>
-      <c r="K8" t="n">
+      <c r="K9" t="n">
         <v>0.06759999999999999</v>
       </c>
-      <c r="L8" t="n">
+      <c r="L9" t="n">
         <v>4.8</v>
       </c>
     </row>
@@ -18448,7 +17602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18506,10 +17660,10 @@
         <v>0.2578</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3781</v>
+        <v>0.3855</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1203</v>
+        <v>0.1278</v>
       </c>
       <c r="F2" t="n">
         <v>15</v>
@@ -18528,16 +17682,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C3" t="n">
-        <v>0.6486</v>
+        <v>0.6441</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4487</v>
+        <v>0.45</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1999</v>
+        <v>-0.1941</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -18546,26 +17700,26 @@
         <v>14</v>
       </c>
       <c r="H3" t="n">
-        <v>24</v>
+        <v>23.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>인력 취약형</t>
+          <t>고수요 유지관리형</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>0.625</v>
+        <v>0.9</v>
       </c>
       <c r="D4" t="n">
-        <v>0.335</v>
+        <v>0.4608</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.29</v>
+        <v>-0.4392</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -18574,26 +17728,26 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>30.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>접근성 보완형</t>
+          <t>인력 취약형</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="C5" t="n">
-        <v>0.5875</v>
+        <v>0.6273</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2838</v>
+        <v>0.3488</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3037</v>
+        <v>-0.2784</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -18602,26 +17756,26 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>5.5</v>
+        <v>30.1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>안정형</t>
+          <t>접근성 보완형</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8318</v>
+        <v>0.5875</v>
       </c>
       <c r="D6" t="n">
-        <v>0.3657</v>
+        <v>0.2935</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4661</v>
+        <v>-0.294</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -18630,6 +17784,34 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>안정형</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>44</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.8273</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.3745</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-0.4528</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>30.1</v>
       </c>
     </row>
@@ -18712,10 +17894,10 @@
         <v>0.3833</v>
       </c>
       <c r="D2" t="n">
-        <v>0.22</v>
+        <v>0.2339</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1633</v>
+        <v>-0.1494</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -18746,10 +17928,10 @@
         <v>0.5</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3314</v>
+        <v>0.3462</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.1686</v>
+        <v>-0.1538</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -18814,10 +17996,10 @@
         <v>0.5417</v>
       </c>
       <c r="D5" t="n">
-        <v>0.3253</v>
+        <v>0.3447</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2164</v>
+        <v>-0.1969</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -18838,29 +18020,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>양산시</t>
+          <t>사천시</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="C6" t="n">
-        <v>0.6636</v>
+        <v>0.5722</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4471</v>
+        <v>0.3628</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2166</v>
+        <v>-0.2094</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -18872,54 +18054,54 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>김해시</t>
+          <t>양산시</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6667</v>
+        <v>0.6636</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4486</v>
+        <v>0.4491</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2181</v>
+        <v>-0.2146</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>사천시</t>
+          <t>김해시</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>0.5722</v>
+        <v>0.6667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3462</v>
+        <v>0.4512</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2261</v>
+        <v>-0.2155</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -18928,13 +18110,13 @@
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -18950,10 +18132,10 @@
         <v>0.5667</v>
       </c>
       <c r="D9" t="n">
-        <v>0.3145</v>
+        <v>0.3339</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.2522</v>
+        <v>-0.2328</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -18984,10 +18166,10 @@
         <v>0.6667</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4002</v>
+        <v>0.4037</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.2664</v>
+        <v>-0.263</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -18996,10 +18178,10 @@
         <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -19008,69 +18190,69 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>창원시</t>
+          <t>밀양시</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="C11" t="n">
-        <v>0.6825</v>
+        <v>0.5833</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4039</v>
+        <v>0.3142</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.2786</v>
+        <v>-0.2692</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>밀양시</t>
+          <t>창원시</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C12" t="n">
-        <v>0.5833</v>
+        <v>0.6825</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2956</v>
+        <v>0.4106</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.2877</v>
+        <v>-0.2719</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -19086,10 +18268,10 @@
         <v>0.5266999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2317</v>
+        <v>0.2428</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.295</v>
+        <v>-0.2839</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -19154,10 +18336,10 @@
         <v>0.6</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2289</v>
+        <v>0.24</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.3711</v>
+        <v>-0.36</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -19188,10 +18370,10 @@
         <v>0.7111</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2759</v>
+        <v>0.2981</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.4352</v>
+        <v>-0.413</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
@@ -19222,10 +18404,10 @@
         <v>0.7167</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2512</v>
+        <v>0.266</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4655</v>
+        <v>-0.4507</v>
       </c>
       <c r="F17" t="n">
         <v>0</v>
@@ -19256,10 +18438,10 @@
         <v>0.6667</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1693</v>
+        <v>0.1804</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4974</v>
+        <v>-0.4863</v>
       </c>
       <c r="F18" t="n">
         <v>0</v>
@@ -19290,10 +18472,10 @@
         <v>0.8222</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2871</v>
+        <v>0.3075</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5351</v>
+        <v>-0.5148</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>

--- a/data/processed/gyeongnam_high_schools_policy_feedback_refined.xlsx
+++ b/data/processed/gyeongnam_high_schools_policy_feedback_refined.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z147"/>
+  <dimension ref="A1:AB147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -550,6 +550,16 @@
           <t>policy_strategy_description</t>
         </is>
       </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>school_latitude</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>school_longitude</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -664,6 +674,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA2" t="n">
+        <v>35.6771045634292</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>127.689678766522</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -778,6 +794,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA3" t="n">
+        <v>35.0635785835826</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>127.961314511887</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -892,6 +914,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA4" t="n">
+        <v>35.2759243075308</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>127.834645753809</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1006,6 +1034,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA5" t="n">
+        <v>35.3181927290868</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>128.507314800732</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1120,6 +1154,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA6" t="n">
+        <v>35.1781655104234</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>127.884595688995</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1234,6 +1274,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA7" t="n">
+        <v>35.2617842731966</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>128.505456829439</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1348,6 +1394,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA8" t="n">
+        <v>35.4141721719533</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>129.174394631319</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1462,6 +1514,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA9" t="n">
+        <v>35.1014406602207</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>128.819449842833</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1576,6 +1634,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA10" t="n">
+        <v>34.7735764364937</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>127.860278182481</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1690,6 +1754,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA11" t="n">
+        <v>35.1696561814851</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>128.281667952322</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1804,6 +1874,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA12" t="n">
+        <v>35.4123803282307</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>129.16999212693</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1918,6 +1994,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA13" t="n">
+        <v>35.3884618653624</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>128.013066406181</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2032,6 +2114,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA14" t="n">
+        <v>35.1186058925822</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>128.488704531696</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2146,6 +2234,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA15" t="n">
+        <v>34.8610875931935</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>128.688426101367</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2260,6 +2354,12 @@
           <t>상담수요가 상대적으로 높고 상담공급이 부족하거나 우선지원점수가 높아 교육청 차원의 우선 지원 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA16" t="n">
+        <v>35.17410570015</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>128.806980454276</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2374,6 +2474,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA17" t="n">
+        <v>35.1981312504391</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>127.927502886143</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2488,6 +2594,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA18" t="n">
+        <v>35.0870312998754</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>128.095881932228</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2602,6 +2714,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA19" t="n">
+        <v>35.1879210181996</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>128.800517861807</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2716,6 +2834,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA20" t="n">
+        <v>35.2020104293439</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>128.803920376232</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2830,6 +2954,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA21" t="n">
+        <v>35.5015485342887</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>128.750923782839</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2944,6 +3074,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA22" t="n">
+        <v>35.2588412928716</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>128.615113707806</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3058,6 +3194,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA23" t="n">
+        <v>35.6002401214951</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>128.381000093523</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3172,6 +3314,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA24" t="n">
+        <v>35.3781486727198</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>129.145038841883</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3286,6 +3434,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA25" t="n">
+        <v>35.6933239305256</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>127.911109160251</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3400,6 +3554,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA26" t="n">
+        <v>35.4918679846425</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>129.087318690399</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3514,6 +3674,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA27" t="n">
+        <v>35.2362292607702</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>128.871079332959</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3628,6 +3794,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA28" t="n">
+        <v>35.1608116244956</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>128.665178884498</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3742,6 +3914,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA29" t="n">
+        <v>35.0440465325682</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>128.063654425894</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3856,6 +4034,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA30" t="n">
+        <v>34.8402101668269</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>128.410152174772</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3970,6 +4154,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA31" t="n">
+        <v>34.8519719382777</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>128.586799629528</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4084,6 +4274,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA32" t="n">
+        <v>34.8540268503364</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>128.424261789301</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4198,6 +4394,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA33" t="n">
+        <v>34.8928558087942</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>128.637235165959</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4312,6 +4514,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA34" t="n">
+        <v>35.2139715595235</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>128.679749626138</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4426,6 +4634,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA35" t="n">
+        <v>35.2395584937856</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>128.853839114441</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4540,6 +4754,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA36" t="n">
+        <v>35.2122838519552</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>128.582107501894</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4654,6 +4874,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA37" t="n">
+        <v>35.3486672549866</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>129.044490862753</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4768,6 +4994,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA38" t="n">
+        <v>35.304767715615</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>128.730004720208</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4882,6 +5114,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA39" t="n">
+        <v>35.2340983095277</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>128.676689060939</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4996,6 +5234,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA40" t="n">
+        <v>35.2268377252433</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>128.693671883358</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -5110,6 +5354,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA41" t="n">
+        <v>35.2000965354561</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>128.080235135137</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -5224,6 +5474,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA42" t="n">
+        <v>35.2215869552647</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>128.704540418351</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -5338,6 +5594,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA43" t="n">
+        <v>35.2318563706783</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>128.861817165997</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -5452,6 +5714,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA44" t="n">
+        <v>34.8633930399088</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>128.646715350706</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -5566,6 +5834,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA45" t="n">
+        <v>35.2229995202771</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>128.574977671659</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -5680,6 +5954,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA46" t="n">
+        <v>35.2094121899909</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>128.5643385877</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -5794,6 +6074,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA47" t="n">
+        <v>35.3356821070533</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>129.01633749355</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5908,6 +6194,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA48" t="n">
+        <v>35.1940098560428</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>128.119014158396</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6022,6 +6314,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA49" t="n">
+        <v>35.2318634188245</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>128.677999454169</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6136,6 +6434,12 @@
           <t>상담수요가 높은 편으로 기존 인프라 보강 또는 상담 프로그램 확대 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA50" t="n">
+        <v>35.2011484686855</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>128.076771617458</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -6250,6 +6554,12 @@
           <t>상담수요가 높지만 공급도 비교적 확보되어 있어 기존 인프라 유지와 프로그램 질 관리가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA51" t="n">
+        <v>35.6910833838131</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>127.900360575893</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -6364,6 +6674,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA52" t="n">
+        <v>35.3333445855717</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>128.710347424496</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -6478,6 +6794,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA53" t="n">
+        <v>35.1758160065726</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>128.152119185535</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -6592,6 +6914,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA54" t="n">
+        <v>35.1886431182834</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>128.556414445409</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -6706,6 +7034,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA55" t="n">
+        <v>35.3241617419833</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>128.24536466054</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -6820,6 +7154,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA56" t="n">
+        <v>35.3727006487523</v>
+      </c>
+      <c r="AB56" t="n">
+        <v>128.713458715223</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -6934,6 +7274,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA57" t="n">
+        <v>34.8574955201497</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>128.012231826952</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -7048,6 +7394,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA58" t="n">
+        <v>35.4010686823669</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>128.842859941817</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -7162,6 +7514,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA59" t="n">
+        <v>35.306322889172</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>127.964302293712</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -7276,6 +7634,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA60" t="n">
+        <v>35.1906552527563</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>128.114310474051</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -7390,6 +7754,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA61" t="n">
+        <v>35.2545664657582</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>128.648822472683</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -7504,6 +7874,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA62" t="n">
+        <v>35.251846702575</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>128.648926140934</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -7618,6 +7994,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA63" t="n">
+        <v>34.9141619755733</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>128.646381185422</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -7732,6 +8114,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA64" t="n">
+        <v>35.2654778374898</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>128.874553443759</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -7846,6 +8234,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA65" t="n">
+        <v>35.2666238467743</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>128.873868698114</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -7960,6 +8354,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA66" t="n">
+        <v>35.2157198462691</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>128.114396937049</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -8074,6 +8474,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA67" t="n">
+        <v>35.2257745182989</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>128.703639766126</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -8188,6 +8594,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA68" t="n">
+        <v>35.2313933541974</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>128.896080879658</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -8302,6 +8714,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA69" t="n">
+        <v>35.1959383430221</v>
+      </c>
+      <c r="AB69" t="n">
+        <v>128.561409708496</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -8416,6 +8834,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA70" t="n">
+        <v>35.3445559166984</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>129.025086059702</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -8530,6 +8954,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA71" t="n">
+        <v>35.2546883556411</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>128.905474404717</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -8644,6 +9074,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA72" t="n">
+        <v>35.2034768863412</v>
+      </c>
+      <c r="AB72" t="n">
+        <v>128.700299729442</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -8758,6 +9194,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA73" t="n">
+        <v>35.259597572054</v>
+      </c>
+      <c r="AB73" t="n">
+        <v>128.343533507993</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -8872,6 +9314,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA74" t="n">
+        <v>35.2322435712973</v>
+      </c>
+      <c r="AB74" t="n">
+        <v>128.887298986012</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -8986,6 +9434,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA75" t="n">
+        <v>35.2821326818366</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>128.403305145623</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -9100,6 +9554,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA76" t="n">
+        <v>35.2259412027856</v>
+      </c>
+      <c r="AB76" t="n">
+        <v>128.597554549774</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -9214,6 +9674,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA77" t="n">
+        <v>35.2470659533563</v>
+      </c>
+      <c r="AB77" t="n">
+        <v>128.596987424283</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -9328,6 +9794,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA78" t="n">
+        <v>34.9397418584784</v>
+      </c>
+      <c r="AB78" t="n">
+        <v>128.089862085081</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -9442,6 +9914,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA79" t="n">
+        <v>35.2273146732954</v>
+      </c>
+      <c r="AB79" t="n">
+        <v>128.66248611227</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -9556,6 +10034,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA80" t="n">
+        <v>35.2382686393143</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>128.852720108492</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -9670,6 +10154,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA81" t="n">
+        <v>34.8392638643409</v>
+      </c>
+      <c r="AB81" t="n">
+        <v>127.902439949009</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -9784,6 +10274,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA82" t="n">
+        <v>35.2265865699855</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>128.661213359055</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -9898,6 +10394,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA83" t="n">
+        <v>35.4737805380356</v>
+      </c>
+      <c r="AB83" t="n">
+        <v>128.76371249178</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -10012,6 +10514,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA84" t="n">
+        <v>35.5136475114705</v>
+      </c>
+      <c r="AB84" t="n">
+        <v>127.721098981375</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -10126,6 +10634,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA85" t="n">
+        <v>35.459602481463</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>128.528366135718</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -10240,6 +10754,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA86" t="n">
+        <v>35.4952119282651</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>128.75593452466</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -10354,6 +10874,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA87" t="n">
+        <v>35.1589968041779</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>128.096534774487</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -10468,6 +10994,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA88" t="n">
+        <v>34.9678060865735</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>128.318571463973</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -10582,6 +11114,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA89" t="n">
+        <v>35.2356856577499</v>
+      </c>
+      <c r="AB89" t="n">
+        <v>128.660267954484</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -10696,6 +11234,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA90" t="n">
+        <v>35.1919473175706</v>
+      </c>
+      <c r="AB90" t="n">
+        <v>128.558406311794</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -10810,6 +11354,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA91" t="n">
+        <v>35.0639132899941</v>
+      </c>
+      <c r="AB91" t="n">
+        <v>127.746167522591</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -10924,6 +11474,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA92" t="n">
+        <v>35.5633248820733</v>
+      </c>
+      <c r="AB92" t="n">
+        <v>128.167910588026</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -11038,6 +11594,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA93" t="n">
+        <v>34.9840664224306</v>
+      </c>
+      <c r="AB93" t="n">
+        <v>128.320164576559</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -11152,6 +11714,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA94" t="n">
+        <v>35.0627934125416</v>
+      </c>
+      <c r="AB94" t="n">
+        <v>127.747228685833</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -11266,6 +11834,12 @@
           <t>전문상담교사 공급 점수가 낮아 전문상담교사 배치 또는 순회상담 연계 검토가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA95" t="n">
+        <v>35.5441279433078</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>128.482361904572</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -11380,6 +11954,12 @@
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA96" t="n">
+        <v>35.4131367653631</v>
+      </c>
+      <c r="AB96" t="n">
+        <v>128.131377427692</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -11494,6 +12074,12 @@
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA97" t="n">
+        <v>35.168250344381</v>
+      </c>
+      <c r="AB97" t="n">
+        <v>128.816494912113</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -11608,6 +12194,12 @@
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA98" t="n">
+        <v>35.7032431448459</v>
+      </c>
+      <c r="AB98" t="n">
+        <v>128.169723246835</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -11722,6 +12314,12 @@
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA99" t="n">
+        <v>35.1124482199264</v>
+      </c>
+      <c r="AB99" t="n">
+        <v>128.749702620096</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -11836,6 +12434,12 @@
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA100" t="n">
+        <v>35.0375271367234</v>
+      </c>
+      <c r="AB100" t="n">
+        <v>127.897878406914</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -11950,6 +12554,12 @@
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA101" t="n">
+        <v>35.3864698488024</v>
+      </c>
+      <c r="AB101" t="n">
+        <v>128.472249036351</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -12064,6 +12674,12 @@
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA102" t="n">
+        <v>34.9867799408032</v>
+      </c>
+      <c r="AB102" t="n">
+        <v>127.8401057682</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -12178,6 +12794,12 @@
           <t>Wee센터 접근성이 낮아 온라인 상담, 이동형 상담 또는 권역별 Wee센터 연계 강화가 필요한 유형</t>
         </is>
       </c>
+      <c r="AA103" t="n">
+        <v>35.6310841440155</v>
+      </c>
+      <c r="AB103" t="n">
+        <v>127.819862703751</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -12292,6 +12914,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA104" t="n">
+        <v>35.1614104475708</v>
+      </c>
+      <c r="AB104" t="n">
+        <v>128.69421717403</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -12406,6 +13034,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA105" t="n">
+        <v>35.1986298205938</v>
+      </c>
+      <c r="AB105" t="n">
+        <v>128.796661767766</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -12520,6 +13154,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA106" t="n">
+        <v>34.8706581895504</v>
+      </c>
+      <c r="AB106" t="n">
+        <v>128.723843213503</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -12634,6 +13274,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA107" t="n">
+        <v>34.9054080732463</v>
+      </c>
+      <c r="AB107" t="n">
+        <v>128.685992495653</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -12748,6 +13394,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA108" t="n">
+        <v>35.2372906222591</v>
+      </c>
+      <c r="AB108" t="n">
+        <v>128.502866678048</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -12862,6 +13514,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA109" t="n">
+        <v>35.1563022977092</v>
+      </c>
+      <c r="AB109" t="n">
+        <v>128.657512286037</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -12976,6 +13634,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA110" t="n">
+        <v>35.1616317053989</v>
+      </c>
+      <c r="AB110" t="n">
+        <v>128.689397121305</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -13090,6 +13754,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA111" t="n">
+        <v>34.8295473421071</v>
+      </c>
+      <c r="AB111" t="n">
+        <v>128.416198016185</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -13204,6 +13874,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA112" t="n">
+        <v>35.2993649147603</v>
+      </c>
+      <c r="AB112" t="n">
+        <v>128.597256204529</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -13318,6 +13994,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA113" t="n">
+        <v>35.2553417806618</v>
+      </c>
+      <c r="AB113" t="n">
+        <v>128.903025424847</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -13432,6 +14114,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA114" t="n">
+        <v>34.8028004626672</v>
+      </c>
+      <c r="AB114" t="n">
+        <v>127.951543024378</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -13546,6 +14234,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA115" t="n">
+        <v>35.1899281873726</v>
+      </c>
+      <c r="AB115" t="n">
+        <v>128.058388901858</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -13660,6 +14354,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA116" t="n">
+        <v>35.3116625047773</v>
+      </c>
+      <c r="AB116" t="n">
+        <v>128.999412374335</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -13774,6 +14474,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA117" t="n">
+        <v>35.3445999186343</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>129.023799031436</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -13888,6 +14594,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA118" t="n">
+        <v>35.3325819198917</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>129.024749057257</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -14002,6 +14714,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA119" t="n">
+        <v>35.2074806828858</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>128.711602507773</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -14116,6 +14834,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA120" t="n">
+        <v>34.869521797481</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>128.413205922052</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -14230,6 +14954,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA121" t="n">
+        <v>35.2483589527865</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>128.676464476886</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -14344,6 +15074,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA122" t="n">
+        <v>35.3297183526478</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>129.018472823442</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -14458,6 +15194,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA123" t="n">
+        <v>35.2504435908382</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>128.875669406317</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -14572,6 +15314,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA124" t="n">
+        <v>35.1774044091928</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>128.11204049237</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -14686,6 +15434,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA125" t="n">
+        <v>35.165171069982</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>128.041709691013</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -14800,6 +15554,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA126" t="n">
+        <v>35.2025448243018</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>128.118939619607</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -14914,6 +15674,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA127" t="n">
+        <v>35.2552857661663</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>128.642705069512</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -15028,6 +15794,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA128" t="n">
+        <v>35.2609674499282</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>128.600515443896</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -15142,6 +15914,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA129" t="n">
+        <v>35.167490215805</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>128.571168595676</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -15256,6 +16034,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA130" t="n">
+        <v>35.4937858569008</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>128.746783406621</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -15370,6 +16154,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA131" t="n">
+        <v>35.0556838834298</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>128.362571773184</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -15484,6 +16274,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA132" t="n">
+        <v>34.8868877467241</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>128.465049182599</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -15598,6 +16394,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA133" t="n">
+        <v>35.6930826295593</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>127.902909247685</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -15712,6 +16514,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA134" t="n">
+        <v>35.2725144557426</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>128.402479825779</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -15826,6 +16634,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA135" t="n">
+        <v>35.2278895605022</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>128.661226194879</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -15940,6 +16754,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA136" t="n">
+        <v>35.2142531567645</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>128.692425901257</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -16054,6 +16874,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA137" t="n">
+        <v>34.9345453558444</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>128.077701048261</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -16168,6 +16994,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA138" t="n">
+        <v>35.197939246733</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>128.559832051422</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -16282,6 +17114,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA139" t="n">
+        <v>35.6903560029964</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>127.904026348041</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -16396,6 +17234,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA140" t="n">
+        <v>35.6930116467922</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>127.909786939337</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -16510,6 +17354,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA141" t="n">
+        <v>35.601349513552</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>128.461516288182</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -16624,6 +17474,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA142" t="n">
+        <v>34.9427082511284</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>128.08481669409</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -16738,6 +17594,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA143" t="n">
+        <v>35.4100168211844</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>127.871096164153</v>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -16852,6 +17714,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA144" t="n">
+        <v>35.5635332170554</v>
+      </c>
+      <c r="AB144" t="n">
+        <v>128.154572589335</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -16966,6 +17834,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA145" t="n">
+        <v>35.5403709329672</v>
+      </c>
+      <c r="AB145" t="n">
+        <v>128.505359650254</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -17080,6 +17954,12 @@
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
       </c>
+      <c r="AA146" t="n">
+        <v>35.3227017364893</v>
+      </c>
+      <c r="AB146" t="n">
+        <v>128.265590219129</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -17193,6 +18073,12 @@
         <is>
           <t>현재 지표상 수요 대비 공급이 상대적으로 안정적인 유형</t>
         </is>
+      </c>
+      <c r="AA147" t="n">
+        <v>35.6767927637267</v>
+      </c>
+      <c r="AB147" t="n">
+        <v>127.912929627495</v>
       </c>
     </row>
   </sheetData>
